--- a/大学心理学2026.xlsx
+++ b/大学心理学2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,23 +742,6 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00020_单选题
-韦纳的归因理论认为归因的稳定性维度是指？（     ）（该题目已移除！）
-A.当事人认为影响其成败因素的来源是来自内因还是外因；
-B.当事人认为影响其成败的因素是否在类似情境具有一致性；
-C.当事人认为影响其成败的因素在性质上是否由个人意愿所决定；
-D.以上都不是；</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
           <t>00021_单选题
 教师在精读教材各个章节时应该关注哪些方面？（     ）
 A.明确教学目标；
@@ -767,14 +750,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>00022_单选题
 布鲁克斯观察到，在日常生活中，部分人预期到将会从事引发焦虑的事情时，会做出一些仪式性行为，来调节焦虑水平，其中仪式性行为不包括？（     ）
@@ -784,14 +767,14 @@
 D.穿经常穿的鞋子；</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>00023_单选题
 热爱学生是大学教师必备的什么素质？（     ）
@@ -801,14 +784,14 @@
 D.职业道德素质；</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>00024_单选题
 教学过程本质上是一个什么样的信息传递过程？（     ）
@@ -818,14 +801,14 @@
 D.固定的；</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>00025_单选题
 “诚实型信任违背”是指？（     ）
@@ -835,14 +818,14 @@
 D.一方因为疏忽导致任务完成不理想；</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>00026_单选题
 大学老师可以通过辅导帮助学生建立良好的室友关系，其中人际认知辅导表现为？（     ）
@@ -852,14 +835,14 @@
 D.帮助大学生认识并觉察自己的社交风格；</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>00027_单选题
 大学生想得到“更为持久的情感联系”，更适合通过何种途径？（     ）
@@ -869,14 +852,14 @@
 D.游戏社交；</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>00028_单选题
 在PPT中使用加粗、高亮、颜色反转等手段的主要目的是什么？（     ）
@@ -886,14 +869,14 @@
 D.提高PPT的制作难度；</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>00029_单选题
 大学生在周末应该如何调整自己的睡眠习惯？（     ）
@@ -903,14 +886,14 @@
 D.缩短睡眠时长，以增加学习时间；</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>00030_单选题
 以下关于运动与认知功能的说法正确的是？（     ）
@@ -920,14 +903,14 @@
 D.运动会减少神经递质的释放；</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>00031_单选题
 教学内容与时俱进，主要可以提高学生的哪种认同感？（     ）
@@ -937,14 +920,14 @@
 D.集体认同感；</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>00032_单选题
 “知−行−信”模式中的“行”代表什么？（     ）
@@ -954,14 +937,14 @@
 D.情感、体验；</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>00033_单选题
 挫折对大学生能够起到的积极作用有？（     ）
@@ -971,14 +954,14 @@
 D.降低大学生的学习效率；</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>00034_单选题
 心理学课程思政的主要目标不包括以下哪一项？（     ）
@@ -988,14 +971,14 @@
 D.承载揭示个体心理活动的机制和规律等方面的理论任务；</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>00035_单选题
 人际关系是在人与人交往过程中形成的，在认知层面上包括（     ）。
@@ -1005,14 +988,14 @@
 D.喜怒哀乐；</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>00036_单选题
 根据成就目标理论，学习目标（掌握目标定向）的核心是什么？（     ）
@@ -1022,14 +1005,14 @@
 D.力求获得好成绩；</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>00037_单选题
 大学教师恰当的自我表露是以下哪种？（     ）
@@ -1039,14 +1022,14 @@
 D.避免分享任何个人经历；</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>00038_单选题
 高颜值取决于面孔吸引力，我们的大脑能以何种时间量级完成对面孔特征与结构的编码？（     ）
@@ -1056,14 +1039,14 @@
 D.分钟级；</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>00039_单选题
 “对不起+承诺”的解释道歉是指？（     ）
@@ -1073,14 +1056,14 @@
 D.承认错误，但拒绝承担责任；</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>00040_单选题
 如何促进大学教师科研团队成员的师德师风建设？（     ）
@@ -1090,14 +1073,14 @@
 D.忽略团队内的知识技能互补；</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>00041_单选题
 创造性地处理教材时，教师应该如何做？（     ）
@@ -1107,14 +1090,14 @@
 D.只使用教材的一半；</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>00042_单选题
 人际关系具有多种类型，同龄人之间或身心发展同水平个体之间在社会交往过程中所建立和发展的人际关系更可能是？（     ）
@@ -1124,14 +1107,14 @@
 D.平行关系；</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>00043_单选题
 根据戴恩等人的研究成果，大学生往往会对哪种人赋予更多美好特征？（     ）
@@ -1141,14 +1124,14 @@
 D.有魅力的；</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>00044_单选题
 以下哪项最准确地描述了“社会性睡眠延迟”？（     ）
@@ -1158,14 +1141,14 @@
 D.周末总是比工作日睡得更晚；</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>00045_单选题
 西方文化下的感恩更注重？（     ）
@@ -1175,14 +1158,14 @@
 D.个体的给予和接受；</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>00046_单选题
 教师在吃透教材的基础上还需要做什么，以下哪项的表述最准确？（     ）
@@ -1192,14 +1175,14 @@
 D.内化作者和编者的意图为自己的教学思想；</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>00047_单选题
 教师如何通过问题驱动策略激发学生的内部学习动机？（     ）
@@ -1209,14 +1192,14 @@
 D.仅在课程结束时讨论学生的问题；</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>00048_单选题
 共生效应凸显了集体对个体成长的重要性，具体表现为？（     ）
@@ -1226,14 +1209,14 @@
 D.人们对他人的某一特征形成好或坏的印象后，这种印象会影响对其他特征的评价；</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>00049_单选题
 平时表现良好但在竞技场上发挥失常，这种效应被心理学家称为？（     ）
@@ -1243,14 +1226,14 @@
 D.巴纳姆效应；</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>00050_单选题
 道歉时下列哪种做法是错误的？（     ）
@@ -1260,14 +1243,14 @@
 D.找借口；</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>00051_单选题
 以下哪项不是高质量睡眠的干扰因素？（     ）
@@ -1277,14 +1260,14 @@
 D.舒适的床上用品；</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>00052_单选题
 大学老师帮助学生战胜“手机分离焦虑”，可以建议学生？（     ）
@@ -1294,14 +1277,14 @@
 D.缩小现实朋友圈；</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>00053_单选题
 以下哪个是关于暴力的心理学实验研究？（     ）
@@ -1311,14 +1294,14 @@
 D.棉花糖实验；</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>00054_单选题
 在PPT中使用颜色和字体变化时，以下哪项不是一个好的实践？（     ）
@@ -1328,14 +1311,14 @@
 D.使用高对比度的颜色搭配提高可读性；</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>00055_单选题
 状态感恩是指个体在受到恩惠时？（     ）
@@ -1345,14 +1328,14 @@
 D.产生的心怀感激的人格特质；</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>00056_单选题
 马斯洛的需求层次理论中，最高层次的需要是什么？（     ）
@@ -1362,14 +1345,14 @@
 D.归属需要；</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>00057_单选题
 “好关系是麻烦出来的”这一观点，体现了什么效应？（     ）
@@ -1379,14 +1362,14 @@
 D.富兰克林效应；</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>00058_单选题
 以下哪项是电子游戏所不具备的能力？（     ）
@@ -1396,14 +1379,14 @@
 D.提高学生的学业成绩；</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>00059_单选题
 学校应如何帮助大学教师处理由于个人情绪压抑导致的心理困扰？（     ）
@@ -1413,14 +1396,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>00060_单选题
 教材在教学中扮演什么角色？（     ）
@@ -1430,14 +1413,14 @@
 D.辅助材料；</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>00061_单选题
 哪种教学策略被认为可以提高学生的批判性思维能力？（     ）
@@ -1447,14 +1430,14 @@
 D.单一视角的讲授；</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>00062_单选题
 持有成长型思维的个体将挑战视为什么？（     ）
@@ -1464,14 +1447,14 @@
 D.浪费时间；</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>00063_单选题
 教师在教学过程中的角色不包括以下哪一项？（     ）
@@ -1481,14 +1464,14 @@
 D.教材内容的完全复制者；</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>00064_单选题
 大学教师压抑情绪带来的不良影响不包括以下哪项？（     ）
@@ -1498,14 +1481,14 @@
 D.增强师生关系；</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>00065_单选题
 根据交往剥夺实验，大学生缺乏人际关系的后果可能是什么？（     ）
@@ -1515,14 +1498,14 @@
 D.增加社会适应能力；</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>00066_单选题
 大学教师在教学中使用讽刺或挖苦的语气进行沟通，这种行为属于哪种层面的不恰当教学行为？（     ）
@@ -1532,14 +1515,14 @@
 D.社会层面；</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>00067_单选题
 目标感作为一种自我组织的生活目标，不具备的功能是？（     ）
@@ -1549,14 +1532,14 @@
 D.提高生活水平；</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>00068_单选题
 教师在教材选择时应该以什么任务为根本？（     ）
@@ -1566,14 +1549,14 @@
 D.减少教学工作量；</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>00069_单选题
 大学生认为自己的能力是可变的，会随着学习而发生改变，在成就目标理论中这是一种什么观点？（     ）
@@ -1583,14 +1566,14 @@
 D.学习实体观；</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>00070_单选题
 大学生在与同伴相处过程中，应该警惕什么倾向？（     ）
@@ -1600,14 +1583,14 @@
 D.抵制诱惑；</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>00071_单选题
 韦纳的归因理论认为归因的可控性维度是指？（     ）
@@ -1617,14 +1600,14 @@
 D.以上都不是；</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>00072_单选题
 积极共同经历对师生关系有什么影响？（     ）
@@ -1634,14 +1617,14 @@
 D.降低师生间的信任；</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>00073_单选题
 教师在没有充分准备的情况下进行教学，这种行为属于不恰当教学行为中的哪一类？（     ）
@@ -1651,14 +1634,14 @@
 D.专业能力缺乏；</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>00074_单选题
 以下关于考试焦虑与学业表现说法正确的是？（     ）
@@ -1668,14 +1651,14 @@
 D.适当的考试焦虑可以促进学业表现；</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>00075_单选题
 根据布拉克特的研究，在人际交往过程中，大学生应提升自身何种能力？（     ）
@@ -1685,14 +1668,14 @@
 D.一般智力；</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>00076_单选题
 哪种神经递质会在我们摄入高脂肪类食物时大量分泌？（     ）
@@ -1702,14 +1685,14 @@
 D.褪黑素；</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>00077_单选题
 教师在重组整合教材时应该考虑哪些因素？（     ）
@@ -1719,14 +1702,14 @@
 D.以上所有因素；</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>00078_单选题
 教师在读懂教材编写的意图时，应该关注哪些意图？（     ）
@@ -1736,14 +1719,14 @@
 D.家长意图；</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>00079_单选题
 不同参与类型对大学生目标感存在影响，以下说法错误的是？（     ）
@@ -1753,14 +1736,14 @@
 D.实习和社会实践则通过深化自我认知，影响大学生的人生目标感；</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>00080_单选题
 网络教学中，教师露脸的方式对学生学习效率的影响是什么？（     ）
@@ -1770,14 +1753,14 @@
 D.没有影响；</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>00081_单选题
 根据加德纳和斯坦博格2005年的研究，大学生在面对风险事件时可以得到什么启发？（     ）
@@ -1787,14 +1770,14 @@
 D.提升理性思考；</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>00082_单选题
 关于暴力的说法，正确的是？（     ）
@@ -1804,14 +1787,14 @@
 D.在体验暴力时不需要考虑社会文化背景所规定的伦理规范；</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>00083_单选题
 马斯洛认为需要的最高层次是哪种需要？（     ）
@@ -1821,14 +1804,14 @@
 D.尊重需要；</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>00084_单选题
 成长型思维干预的目的是什么？（     ）
@@ -1838,14 +1821,14 @@
 D.减少学生的压力；</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>00085_单选题
 人际交往过程中，颜值固然重要，但归根到底还是看修养，以下何种品质不利于大学生保持稳定的友谊？（     ）
@@ -1855,14 +1838,14 @@
 D.自私；</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>00086_单选题
 大学教师团队建设的路径中，以下哪项不是其有效的策略？（     ）
@@ -1872,14 +1855,14 @@
 D.注重教师团队精神的建设；</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>00087_单选题
 “明明可以靠脸吃饭的，却偏要靠实力”，这句流行语透露的信息不包括？（     ）
@@ -1889,14 +1872,14 @@
 D.对多元化成功的认同；</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>00088_单选题
 在面对他人评价时，大学生往往更倾向于接受哪种评价方式？（     ）
@@ -1906,14 +1889,14 @@
 D.先贬后褒；</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>00089_单选题
 焦虑是大学生活中不可避免的情绪，长期性的焦虑带来的结果通常是？（     ）
@@ -1923,14 +1906,14 @@
 D.以上都不正确；</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>00090_单选题
 研究发现，低强度运动与提升主观幸福感和降低抑郁水平的关系为？（     ）
@@ -1940,14 +1923,14 @@
 D.无关；</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>00091_单选题
 人体在哪个睡眠阶段能够学习？（     ）
@@ -1957,14 +1940,14 @@
 D.所有睡眠阶段；</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>00092_单选题
 拥有良好同伴关系的大学生通常表现出？（     ）
@@ -1974,14 +1957,14 @@
 D.较高的抑郁风险；</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>00093_单选题
 课程思政的主要目的是什么？（     ）
@@ -1991,14 +1974,14 @@
 D.增加学生的课外活动；</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>00094_单选题
 通常来说，什么年级的大学生人生目标感相对较低？（     ）
@@ -2008,14 +1991,14 @@
 D.大四学生；</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>00095_单选题
 教师在课堂上频繁使用手机，忽视学生的学习状态，这种行为属于教师失范行为中的哪一类？（     ）
@@ -2025,14 +2008,14 @@
 D.专业能力缺乏；</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>00096_单选题
 在教师在课堂教学中自我表露对学生评价的影响的研究中，以下哪种情况的教师获得了学生更高的评价？（     ）
@@ -2042,14 +2025,14 @@
 D.教师表露工作的评课片段；</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>00097_单选题
 拥有攻击型竞争心理的大学生发现自己成绩不如他人时，可能表现出何种行为？（     ）
@@ -2059,14 +2042,14 @@
 D.帮助他人；</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>00098_单选题
 大学教师在教材选择时应该确保教材的哪些特性？（     ）
@@ -2076,14 +2059,14 @@
 D.所有以上因素；</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>00099_单选题
 研究发现，助人的次数越多，助人者越能够怎样看待问题？（     ）
@@ -2093,14 +2076,14 @@
 D.更主观；</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>00100_单选题
 大学老师需要引导学生调整认知，制定合理目标，以下哪项说法是错误的？（     ）
@@ -2110,14 +2093,14 @@
 D.教师应该鼓励学生用辩证和发展的眼光看待自己；</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>00101_单选题
 我们的生物钟节律与哪个方面有很大的关联？（     ）
@@ -2127,14 +2110,14 @@
 D.记忆力；</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>00102_单选题
 以下哪项不属于大学教师向学生强调管理压力重要性的范畴？（     ）
@@ -2144,14 +2127,14 @@
 D.引导学生定期回顾自己的目标进展和生活方向；</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>00103_单选题
 在教材的创造性处理中，教师不应该采取哪种做法？（     ）
@@ -2161,14 +2144,14 @@
 D.延伸拓展教材内容；</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>00104_单选题
 情境修正要求个体迅速而灵活地产生可能改变情境进程的替代行动，该情景通常发生在何时？（     ）
@@ -2178,14 +2161,14 @@
 D.很远的过去；</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>00105_单选题
 β内啡肽的功能主要包括？（     ）
@@ -2195,14 +2178,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>00106_单选题
 教师的人际沟通能力不足或是沟通技巧欠缺可能引发多种不恰当的教学行为，以下哪项不是由此引发的？（     ）
@@ -2212,14 +2195,14 @@
 D.增加学生的自主性；</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>00107_单选题
 大学教师引导学生发展目标感具有重要意义，以下哪项不是合适的途径？（     ）
@@ -2229,14 +2212,14 @@
 D.以核心价值观来指导他们的行为和决定；</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>00108_单选题
 安德鲁的实验证明？（     ）
@@ -2246,14 +2229,14 @@
 D.暴力成分与可以吸引更多的玩家；</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>00109_单选题
 以下哪项不是培养大学生感恩的活动？（     ）
@@ -2263,14 +2246,14 @@
 D.围棋比赛；</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>00110_单选题
 教师利用自己的职位影响力，向学生或家长索取利益，这种行为属于教师失范行为中的哪一类？（     ）
@@ -2280,14 +2263,14 @@
 D.专业能力缺乏；</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>00111_单选题
 光环效应是一种有偏差的主观印象，以下哪种方式不能帮助大学生避免光环效应？（     ）
@@ -2297,14 +2280,14 @@
 D.避免以貌取人；</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>00112_单选题
 大学老师可以通过辅导帮助学生建立良好的室友关系，其中人际行为辅导表现为？（     ）
@@ -2314,14 +2297,14 @@
 D.帮助大学生认识并觉察自己的社交风格；</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>00113_单选题
 心理学家马修·蒙托亚的一项元分析发现人际交往会与什么因素显著相关？（     ）
@@ -2331,14 +2314,14 @@
 D.变异性；</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>00114_单选题
 大学生适量运动具有重要意义，以下哪种关于运动的观点是不正确的？（     ）
@@ -2348,14 +2331,14 @@
 D.运动能降低我们的心理压力；</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>00115_单选题
 什么是实现运动效果的核心要素？（     ）
@@ -2365,14 +2348,14 @@
 D.制定目标；</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>00116_单选题
 以下哪项对感恩子成分的划分更为准确？（     ）
@@ -2382,14 +2365,14 @@
 D.特质感恩与个体感恩；</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>00117_单选题
 以下哪一种行为是行动式自我妨碍？（     ）
@@ -2399,14 +2382,14 @@
 D.肚子疼；</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>00118_单选题
 自我决定理论中，人们的基本心理需求是哪三种？（     ）
@@ -2416,14 +2399,14 @@
 D.独立性、能力感、连接感；</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>00119_单选题
 下列说法当中错误的是？（     ）
@@ -2433,14 +2416,14 @@
 D.教师应该学会放下高冷，作真实有温度的教师；</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>00120_单选题
 韦纳的归因理论将归因分为哪种维度？（     ）
@@ -2450,14 +2433,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>00121_单选题
 教师在紧急情况下忽视学生安全，这种行为属于教师失范行为中的哪一类？（     ）
@@ -2467,14 +2450,14 @@
 D.专业能力缺乏；</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>00122_单选题
 相比于恶性竞争，大学生拥有理性竞争意识更可能有何种表现？（     ）
@@ -2484,14 +2467,14 @@
 D.追求安逸；</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>00123_单选题
 大学教师科研团队的建设过程中，如何处理教学与科研的关系？（     ）
@@ -2501,14 +2484,14 @@
 D.教学与科研完全分离；</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>00124_单选题
 根据“友谊的小船”故事，大学生在集体生活中应该做到？（     ）
@@ -2518,14 +2501,14 @@
 D.互帮互助；</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>00125_单选题
 在大学师生交往中，大学生最喜欢下列哪种教师？（     ）
@@ -2535,14 +2518,14 @@
 D.对自己的喜欢或赞扬时高时低的大学教师；</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>00126_单选题
 教师在批改学生作业时，经常使用贬低性语言，这种行为属于不恰当教学行为中的哪一类？（     ）
@@ -2552,14 +2535,14 @@
 D.专业能力缺乏；</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>00127_单选题
 面孔吸引力在人际交往具有重要意义，大学生应如何看待自身面孔吸引力？（     ）
@@ -2569,14 +2552,14 @@
 D.自我怀疑；</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>00128_单选题
 大学生通过游戏的方式来处理暴力冲动，这在精神分析中属于什么防御机制？（     ）
@@ -2586,14 +2569,14 @@
 D.反向生成；</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>00129_单选题
 相较而言，哪种教学方式更能促进学生的参与度和兴趣？（     ）
@@ -2603,14 +2586,14 @@
 D.仅探索；</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>00130_单选题
 下列不属于良好大学师生关系的特点的选项是？（     ）
@@ -2620,14 +2603,14 @@
 D.敬而远之；</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>00131_单选题
 哪种神经递质增加是运动带来欣快感的原因？（     ）
@@ -2637,14 +2620,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>00132_单选题
 拥有逃避型竞争心理的大学生发现自己成绩不如他人时，可能表现出何种行为？（     ）
@@ -2654,14 +2637,14 @@
 D.帮助他人；</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>00133_单选题
 道歉对信任修复的作用主要体现在哪两个方面？（     ）
@@ -2671,14 +2654,14 @@
 D.提高双方的沟通效率和降低双方的冲突概率；</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>00134_单选题
 对于大学生来说，下面有关睡眠与学习关系的选项中哪项是正确的？（     ）
@@ -2688,14 +2671,14 @@
 D.在深度非快速眼动阶段大学生有可能发生学习行为；</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>00135_单选题
 大学生网络成瘾存在较大危害，以下何种不是网络成瘾的保护性因素？（     ）
@@ -2705,14 +2688,14 @@
 D.积极的社交活动；</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>00136_单选题
 “知−行−信”模式中的“知”代表什么？（     ）
@@ -2722,14 +2705,14 @@
 D.情感、体验；</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>00137_单选题
 自我妨碍的发展是为了可以将失败归咎于什么原因？（     ）
@@ -2739,14 +2722,14 @@
 D.努力；</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>00138_单选题
 通过问题驱动增强学生的求知欲，这种方法主要激发了哪种学习动机？（     ）
@@ -2756,14 +2739,14 @@
 D.个人动机；</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>00139_单选题
 费什巴赫提出的宣泄假说可以支持以下哪个观点？（     ）
@@ -2773,14 +2756,14 @@
 D.暴力游戏可能会增加大学生攻击冲动；</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>00140_单选题
 大学生拥有良好的睡眠通过何种途径帮助减少拖延行为？（     ）
@@ -2790,14 +2773,14 @@
 D.减少作息的规律性；</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>00141_单选题
 以下不是网络成瘾表现的是？（     ）
@@ -2807,14 +2790,14 @@
 D.明显身体损伤；</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>00142_单选题
 从心理学的角度来看，“高冷”实际上是？（     ）
@@ -2824,14 +2807,14 @@
 D.神秘；</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>00143_单选题
 教学内容与时俱进的目的是什么？（     ）
@@ -2841,14 +2824,14 @@
 D.降低课程的相关性；</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>00144_单选题
 教师在吃透教材时，应该如何处理教材中的知识点？（     ）
@@ -2858,14 +2841,14 @@
 D.只关注教材中的难点；</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>00145_单选题
 运动的好处主要包括？（     ）
@@ -2875,14 +2858,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>00146_单选题
 “学然后知不足，教然后知困”体现了师生关系具有什么样的特点？（     ）
@@ -2892,14 +2875,14 @@
 D.教学相长；</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>00147_单选题
 虚拟仿真实验教学课程属于哪种课程形式？（     ）
@@ -2909,14 +2892,14 @@
 D.实践课程；</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>00148_单选题
 我们需要特别关注暴力内容存在于？（     ）
@@ -2926,14 +2909,14 @@
 D.日常生活中；</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>00149_单选题
 成就目标理论中，学习目标（掌握目标定向）的核心是什么？（     ）
@@ -2943,14 +2926,14 @@
 D.力求获得好成绩；</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>00150_单选题
 倾听的关键不包括以下哪项？（     ）
@@ -2960,14 +2943,14 @@
 D.严厉批评；</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>00151_单选题
 以下关于教师向大学生解释设定目标的重要性的说法，错误的是？（     ）
@@ -2977,14 +2960,14 @@
 D.说明将长远目标与近期目标结合的重要性；</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>00152_单选题
 心理学“知−行−信”课程思政模式，“知”的层面需要做到什么？（     ）
@@ -2994,14 +2977,14 @@
 D.增强体验感；</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>00153_单选题
 大学教师融入教学科研团队的最佳方式是？（     ）
@@ -3011,14 +2994,14 @@
 D.通过避免团队冲突保持个人形象；</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>00154_单选题
 大学师生之间应建立何种师生关系？（     ）
@@ -3028,14 +3011,14 @@
 D.亲而有间；</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>00155_单选题
 学生帮助教师，对学生自身有什么益处？（     ）
@@ -3045,14 +3028,14 @@
 D.会让学生产生厌恶感；</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>00156_单选题
 急性运动时，（     ）神经递质的增加会改善个体的失眠情况？
@@ -3062,14 +3045,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>00157_单选题
 课程思政建设是全面提高哪个方面的重要任务？（     ）
@@ -3079,14 +3062,14 @@
 D.教师的数量；</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>00158_单选题
 大学生不正当竞争心理中不包括哪种类型？（     ）
@@ -3096,14 +3079,14 @@
 D.逃避型竞争；</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>00159_单选题
 自我妨碍在个体面临潜在的学业或表现失败时的作用是？（     ）
@@ -3113,14 +3096,14 @@
 D.减少努力；</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>00160_单选题
 大学教师之间应该如何相互影响？（     ）
@@ -3130,14 +3113,14 @@
 D.避免个人情感的交流；</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>00161_单选题
 我国提倡的平等民主的师生关系，主要是指师生之间的什么平等？（     ）
@@ -3147,14 +3130,14 @@
 D.义务平等；</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>00162_单选题
 大学教师应如何处理和大学生的意见分歧？（     ）
@@ -3164,14 +3147,14 @@
 D.忽略学生的意见，按自己的想法行事；</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>00163_单选题
 心理学“知−行−信”课程思政模式，“信”的层面需要做到什么？（     ）
@@ -3181,14 +3164,14 @@
 D.增强体验感；</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>00164_单选题
 一般情况下，网络课程中教师形象大小怎么呈现最有利于学生学习？（     ）
@@ -3198,14 +3181,14 @@
 D.不呈现最好；</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>00165_单选题
 当教师与学生发生矛盾时，以下哪种做法是合理的宣泄方式？（     ）
@@ -3215,14 +3198,14 @@
 D.对学生进行惩罚；</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>00166_单选题
 根据克鲁姆等人2013年的研究，在人际交往过程中，大学生应该做到？（     ）
@@ -3232,14 +3215,14 @@
 D.冷漠待人；</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>00167_单选题
 大学教师在引导学生淡化个别考试结果的过程中，应该注意的是（     ）。
@@ -3249,14 +3232,14 @@
 D.教师应帮助学生建立终身学习意识；</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>00168_单选题
 在PPT中使用导读的主要目的是什么？（     ）
@@ -3266,14 +3249,14 @@
 D.展示教师的创造力；</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>00169_单选题
 教师工作不尽职，包括毫无准备地去上课、迟到甚至忘记上课等，这属于以下哪个层面的不恰当教学行为？（     ）
@@ -3283,14 +3266,14 @@
 D.社会层面；</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>00170_单选题
 高冷的人通常会给他人什么样的感觉？（     ）
@@ -3300,14 +3283,14 @@
 D.主动；</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>00171_单选题
 大学生认为自己的能力是固定的，不会随学习而发生改变，在德韦克的成就目标理论中这是一种什么观？（     ）
@@ -3317,14 +3300,14 @@
 D.学习实体观；</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>00172_单选题
 以下哪种说法是错误的？（     ）
@@ -3334,14 +3317,14 @@
 D.道歉只有在被违背者原谅的情况下才有效；</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>00173_单选题
 学校建立全面的评价体系对于培养大学生的理性竞争意识具有重要意义，该评价体系的指标不应包括？（     ）
@@ -3351,14 +3334,14 @@
 D.社会地位；</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>00174_单选题
 以下哪种措施能减轻大学生面临的评价性威胁？（     ）
@@ -3368,14 +3351,14 @@
 D.单项评价；</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>00175_单选题
 目标感是一种？（     ）
@@ -3385,14 +3368,14 @@
 D.心理韧性；</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>00176_单选题
 根据詹森效应，詹森最应该如何找回状态？（     ）
@@ -3402,14 +3385,14 @@
 D.获得观众的鼓励；</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>00177_单选题
 大学生依据当下情境特点和需求选择适当的策略发生在情绪调节的何种阶段？（     ）
@@ -3419,14 +3402,14 @@
 D.控制阶段；</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>00178_单选题
 心理学“知−行−信”课程思政模式，“行”的层面需要做到什么？（     ）
@@ -3436,14 +3419,14 @@
 D.增强体验感；</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>00179_单选题
 大学教师在遇到教学困难时，以下哪种做法有助于排解情绪？（     ）
@@ -3453,14 +3436,14 @@
 D.独自承受压力，不与他人交流；</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>00180_单选题
 基于“社交媒体点赞”研究结果，如果大学生的朋友圈收到很多“赞”时，大脑什么区域可能显著激活？（     ）
@@ -3470,14 +3453,14 @@
 D.小脑；</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>00181_单选题
 如果大学生之间产生矛盾，以下哪种道歉内容相对最容易被接受？（     ）
@@ -3487,14 +3470,14 @@
 D.“对不起，是因为我的失误导致的结果，我以后会尽量避免的”；</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>00182_单选题
 面孔吸引力是指目标人物的面孔所诱发的一种积极愉悦的情绪体验，可以促使大学生产生何种意愿？（     ）
@@ -3504,14 +3487,14 @@
 D.远离；</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>00183_单选题
 与好友结伴运动或在音乐的陪伴下锻炼的主要作用包括？（     ）
@@ -3521,14 +3504,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>00184_单选题
 教师在课堂上使用手势的主要目的是什么？（     ）
@@ -3538,14 +3521,14 @@
 D.增加学生的紧张感；</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>00185_单选题
 成长型思维干预中，参与者通过哪种方式将成长型思维内化并应用于实际情境中？（     ）
@@ -3555,14 +3538,14 @@
 D.通过完成数学题目；</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>00186_单选题
 大学生是大学教育活动的主体，所以大学教师要充分发挥学生的什么特点？（     ）
@@ -3572,14 +3555,14 @@
 D.互动性；</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>00187_单选题
 身体上的温暖可以促进个体对人际交往中什么的感知？（     ）
@@ -3589,14 +3572,14 @@
 D.高冷；</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>00188_单选题
 大学教师引导学生发展目标感具有重要意义，以下哪项不利于学生目标感的建立？（     ）
@@ -3606,14 +3589,14 @@
 D.以核心价值观来指导他们的行为和决策；</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>00189_单选题
 压力是把双刃剑，以下关于压力的说法正确的是？（     ）
@@ -3623,14 +3606,14 @@
 D.适度的压力有利于提升个体智力；</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B188" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>00190_单选题
 马斯洛需求层次理论提到的需求不包括什么？（     ）
@@ -3640,14 +3623,14 @@
 D.尊重需要；</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B189" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>00191_单选题
 “内卷”现象对大学生有何影响？（     ）
@@ -3657,14 +3640,14 @@
 D.追求个性发展；</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>00192_单选题
 过分概括，指将个别事件视为普遍现象，进而放大自身不良情绪。以下哪个例子不能体现该现象？（     ）
@@ -3674,14 +3657,14 @@
 D.小明认为一道错题是自己没有努力学习的表现；</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>00193_单选题
 帮助大学生建立理性竞争意识，师生、生生间应该保持何种氛围？（     ）
@@ -3691,14 +3674,14 @@
 D.同质性；</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>00194_单选题
 根据德韦克的理论，持有固定型思维的大学生会认为能力是什么？（     ）
@@ -3708,14 +3691,14 @@
 D.仅与环境有关；</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>00195_单选题
 人际关系是在人与人交往过程中形成的，在行为层面上包括？（     ）
@@ -3725,14 +3708,14 @@
 D.喜怒哀乐；</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>00196_单选题
 根据耶克斯-多德森定律，大学生想要获得最佳的学习效率，应该把唤醒水平置于何种程度？（     ）
@@ -3742,14 +3725,14 @@
 D.无强度；</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B195" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>00197_单选题
 教师利用家长的关系做私事、与学生的关系超出了师生关系属于以下哪个层面的不恰当教学行为？（     ）
@@ -3759,14 +3742,14 @@
 D.社会层面；</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B196" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>00198_单选题
 心理学课程思政的优势体现在哪个方面？（     ）
@@ -3776,14 +3759,14 @@
 D.专注于应用技能；</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>00199_单选题
 作为大学教师，如果学生不喜欢自己，可以怎么做？（     ）
@@ -3793,14 +3776,14 @@
 D.找机会请学生帮忙处理一些小事；</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>00200_单选题
 大学生的人际交往过程中，下列哪个道歉方式对修复信任的效果相对较差？（     ）
@@ -3810,14 +3793,14 @@
 D.承诺不会再犯该错误；</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B199" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>00201_单选题
 大学生室友关系多种多样，以下哪种关系更可能导致不良后果？（     ）
@@ -3827,14 +3810,14 @@
 D.礼貌相处型；</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>00202_单选题
 对于大学生来说，以下哪项关于睡眠的描述最为准确？（     ）
@@ -3844,14 +3827,14 @@
 D.睡眠时长的增加不一定保证睡眠质量；</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>00203_单选题
 教师在学生遇到紧急情况时，未能及时提供帮助，这种行为属于教师失范行为中的哪一类？（     ）
@@ -3861,14 +3844,14 @@
 D.专业能力缺乏；</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>00204_单选题
 以下哪一种行为是自陈式自我妨碍？（     ）
@@ -3878,14 +3861,14 @@
 D.吃午饭；</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>00205_单选题
 独立的协作模式对教师团队成员的要求不包括哪项？（     ）
@@ -3895,14 +3878,14 @@
 D.各做各的任务，不关心其他成员的工作；</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>00206_单选题
 光环效应也称晕轮效应，是一种影响人际知觉的心理现象，表现为？（     ）
@@ -3912,14 +3895,14 @@
 D.初次对人知觉时形成的印象最深刻；</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>00207_单选题
 师生之间的现实关系是不断变化和丰富多彩的，教育教学中的师生关系本质上是什么？（     ）
@@ -3929,14 +3912,14 @@
 D.以平等人格和情感交流为基础的朋友关系；</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>00208_单选题
 以下哪个不是学生群体日常生活中主要的压力来源？（     ）
@@ -3946,14 +3929,14 @@
 D.师生关系；</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>00209_单选题
 富兰克林效应是指什么？（     ）
@@ -3963,14 +3946,14 @@
 D.与他人合作会增进彼此的关系；</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>00210_单选题
 何种程度的动机会使大学生处于过度焦虑和紧张的状态，干扰记忆、思维功能？（     ）
@@ -3980,14 +3963,14 @@
 D.极低；</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>00211_单选题
 大学教师科研适应中，以下哪项是提升科研能力的有效措施？（     ）
@@ -3997,14 +3980,14 @@
 D.避免反思，只关注教学任务的完成；</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>00212_单选题
 大学教师或大学生可采取多种行动来应对消极情绪，以下哪种行动属于认知重评策略？（     ）
@@ -4014,14 +3997,14 @@
 D.用积极视角重新评估情绪事件；</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>00213_单选题
 习惯于网络聊天的大学生，面对面交流的能力很可能会？（     ）
@@ -4031,14 +4014,14 @@
 D.减弱；</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>00214_单选题
 大学生应该如何与大学教师相处？（     ）
@@ -4048,14 +4031,14 @@
 D.仅在需要帮助时才与教师交流；</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>00215_单选题
 以下哪个不属于SMART原则？（     ）
@@ -4065,14 +4048,14 @@
 D.不可衡量性；</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>00216_单选题
 大学生处于何种校园氛围不容易产生恶性竞争意识？（     ）
@@ -4082,14 +4065,14 @@
 D.多压力源；</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>00217_单选题
 在融入教学科研团队时，大学教师应当怎么做？（     ）
@@ -4099,14 +4082,14 @@
 D.保持个人独立性，不参加任何团队活动；</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>00218_单选题
 塞利格曼等人于2005年对成人样本进行为期一周的“感恩拜访”干预，结果发现被试报告了更多的？（     ）
@@ -4116,14 +4099,14 @@
 D.幸福感；</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>00219_单选题
 大学老师在师生关系中应避免以下哪种行为？（     ）
@@ -4133,14 +4116,14 @@
 D.尊重学生的个体差异；</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>00220_单选题
 教师的个人习惯中，以下哪项最不可能直接导致不恰当教学行为？（     ）
@@ -4150,14 +4133,14 @@
 D.个人情绪的波动；</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>00221_单选题
 麻烦学生也需要掌握一定的技巧，以下哪一项说法是不正确的？（     ）
@@ -4167,14 +4150,14 @@
 D.要考虑时机和场合；</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>00222_单选题
 关于大学教师自我表露描述不正确的是？（     ）
@@ -4184,14 +4167,14 @@
 D.大学教师可以随意分享任何内容；</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>00223_单选题
 大学生进行自信训练有利于？（     ）
@@ -4201,14 +4184,14 @@
 D.面对挑战时选择逃避；</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>00224_单选题
 苏霍姆林斯基认为，对某些学生来说，老师的什么态度可能会毁掉一生？（     ）
@@ -4218,14 +4201,14 @@
 D.支持；</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>00225_单选题
 运动时，（     ）含量会上升会让我们感到愉悦？
@@ -4235,14 +4218,14 @@
 D.以上都不是；</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>00226_单选题
 最有利于大学生发展的师生关系类型是哪种？（     ）
@@ -4252,14 +4235,14 @@
 D.管理型；</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>00227_单选题
 “社会性睡眠延迟”是谁提出的？（     ）
@@ -4269,14 +4252,14 @@
 D.吉拉尔；</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>00228_单选题
 线上露脸课程的“眼睛效应”指的是什么？（     ）
@@ -4286,14 +4269,14 @@
 D.学生通过视频观察教师的眼神变化；</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>00229_单选题
 对于大学生来说，下列关于詹森效应的描述哪一项是不正确的？（     ）
@@ -4303,14 +4286,14 @@
 D.詹森效应与大学生所承受的压力水平相关；</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>00230_单选题
 高冷的大学教师通常会给学生什么样的感觉？（     ）
@@ -4320,14 +4303,14 @@
 D.主动；</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>00231_单选题
 教师在网络教学中应如何使用自己的形象？（     ）
@@ -4337,14 +4320,14 @@
 D.根据教师个人喜好决定；</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>00232_单选题
 人际吸引是个体与他人之间情感上相互喜欢、相互需要，依赖的状态，以下哪种是最高程度的人际吸引？（     ）
@@ -4354,14 +4337,14 @@
 D.亲和；</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>00233_单选题
 根据多拉德和米勒提出的挫折引发攻击行为的理论，对于大学生玩家有什么启示？（     ）
@@ -4371,14 +4354,14 @@
 D.游戏完全不含暴力成分，玩家也可能因为输掉游戏而产生挫败感，继而带来攻击情绪；</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>00234_单选题
 詹森效应在大学生身上可表现为什么？（     ）
@@ -4388,14 +4371,14 @@
 D.平时表现一般在竞赛中发挥也一般；</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>00235_单选题
 以下哪种措施能增强大学生的自我效能感？（     ）
@@ -4405,14 +4388,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>00236_单选题
 友谊通常不能满足大学生的什么需求？（     ）
@@ -4422,14 +4405,14 @@
 D.个人成长；</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>00237_单选题
 当一株植物单独生长时，就会显得矮小和单调；而与众多的同类植物在一起共同生长时，就会显得枝繁叶茂、生机盎然，这种效应是？（     ）
@@ -4439,14 +4422,14 @@
 D.后摄效应；</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>00238_单选题
 韦纳的归因理论认为归因的因素源维度是指？（     ）
@@ -4456,14 +4439,14 @@
 D.以上都不是；</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>00239_单选题
 认知改变是关于如何以不同的视角来看待已经产生的情绪，以下哪种策略属于认知改变范畴？（     ）
@@ -4473,14 +4456,14 @@
 D.标签；</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>00240_单选题
 根据耶克斯-多德森定律，大学生的学习动机水平与学习效率之间可能是一种什么关系？（     ）
@@ -4490,14 +4473,14 @@
 D.M型；</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>00241_单选题
 大学生通过调整认知，制定合理目标可以获得？（     ）
@@ -4507,14 +4490,14 @@
 D.更低的效能感；</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>00242_单选题
 大学生“内卷”是一个普遍现象，以下哪种现象不符合“内卷”？（     ）
@@ -4524,14 +4507,14 @@
 D.大学生制定合理学习时间，每天按部就班的完成学习任务；</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>00243_单选题
 压力时大学生活中不可避免的，以下关于压力的说法正确的是？（     ）
@@ -4541,14 +4524,14 @@
 D.压力对我们没有作用；</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>00244_单选题
 以下哪项是提升大学教师科研能力的关键策略？（     ）
@@ -4558,14 +4541,14 @@
 D.限制教师的学术交流；</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>00245_单选题
 基于科恩2017年的研究，语速和信息传输之间可能是什么关系？（     ）
@@ -4575,14 +4558,14 @@
 D.大学教师说话速度与信息的传输量不存在线性关系；</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>00246_单选题
 为建立良好的师生关系，以下大学教师使用的方法不正确的是哪项？（     ）
@@ -4592,14 +4575,14 @@
 D.明确立下自己的界限；</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>00247_单选题
 教师应该帮助大学生克服詹森效应，以下做法不合适的是？（     ）
@@ -4609,14 +4592,14 @@
 D.促使学生努力学习，鼓励挑灯夜读；</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>00248_单选题
 为了增强学生的自我决定感，大学教师可以采取以下哪种措施？（     ）
@@ -4626,14 +4609,14 @@
 D.限制学生的课堂参与；</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>00249_单选题
 以下哪种感恩的特点包含能够持续一段时间的心境？（     ）
@@ -4643,14 +4626,14 @@
 D.特质感恩；</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>00250_单选题
 相较而言，哪种线上课程的展示方式对中国学生的学习成果影响最好？（     ）
@@ -4660,14 +4643,14 @@
 D.录制整个课堂活动的线上课程；</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>00251_单选题
 网络成瘾对个体职业满意度和心理健康均存在？（     ）
@@ -4677,14 +4660,14 @@
 D.不显著的正面影响；</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>00252_单选题
 大学生每天留出一定时间和家人、朋友面对面交流通常有什么作用？（     ）
@@ -4694,14 +4677,14 @@
 D.加剧精神压力；</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>00253_单选题
 高情绪智力的大学生通常拥有更好的人际关系，可能的原因是？（     ）
@@ -4711,14 +4694,14 @@
 D.拥有更低的人际支持水平；</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>00254_单选题
 网络教学中教师露脸的主要优点是什么？（     ）
@@ -4728,14 +4711,14 @@
 D.降低视频制作成本；</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>00255_单选题
 美国学者安德森发现了6种影响人际关系的人格品质，何种最为可贵？（     ）
@@ -4745,14 +4728,14 @@
 D.忠诚；</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>00256_单选题
 根据《日本新华侨报》的刊文，智能时代的人们比过去任何一个时代的人都感到？（     ）
@@ -4762,14 +4745,14 @@
 D.绝望；</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>00257_单选题
 教师在“读”教材时应该采用哪些方法？（     ）
@@ -4779,14 +4762,14 @@
 D.以上都是；</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>00258_单选题
 根据班杜拉的波比娃娃实验，以下说法正确的是？（     ）
@@ -4796,14 +4779,14 @@
 D.儿童的观察学习受到亲密关系的影响；</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>00259_单选题
 根据成就目标理论，以下哪种描述表现出大学生是成绩目标定向的？（     ）
@@ -4813,14 +4796,14 @@
 D.对学习本身感兴趣，而非结果；</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>00260_多选题
 美丽的面孔之所以吸引人，可能是因为它们具有哪些特征？（     ）
@@ -4830,14 +4813,14 @@
 D.激发了人类本能的冲动；</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>00261_多选题
 韦纳的归因理论认为归因的维度主要包括？（     ）
@@ -4847,14 +4830,14 @@
 D.当事人认为影响其成败的因素是固定的；</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>00262_多选题
 在班杜拉的波比娃娃实验中，儿童出现了哪些表现？（     ）
@@ -4864,14 +4847,14 @@
 D.强化了攻击行为；</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>00263_多选题
 学习动机的两个基本成分是？（     ）
@@ -4881,14 +4864,14 @@
 D.学习期待；</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>00264_多选题
 在教学中，哪些方法可以用来尊重和提升学生的主体地位？（     ）
@@ -4898,14 +4881,14 @@
 D.及时对学生的疑问和错误进行反馈和调整；</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>00265_多选题
 在“知−行−信”课程思政模式中，“行”的层面强调“行动导向，学以致用”。大学教师可以通过哪些具体方法来实现这一教学要求？（     ）
@@ -4915,14 +4898,14 @@
 D.要引导关注社会热点与现实问题，开展调查研究；</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>00266_多选题
 关于游戏中的暴力内容，下面哪些观点或说法是片面的？（     ）
@@ -4932,14 +4915,14 @@
 D.暴力游戏只会增加犯罪冲动；</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>00267_多选题
 大学教师可以通过哪些不同的阅读策略来深入理解教材内容？（     ）
@@ -4949,14 +4932,14 @@
 D.精读；</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>00268_多选题
 教师在创造性地处理教材时，应该避免哪些情况？（     ）
@@ -4966,14 +4949,14 @@
 D.教材内容的拓展和补充；</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>00269_多选题
 在大学生活中，哪些人际关系可能显得尤为重要？（     ）
@@ -4983,14 +4966,14 @@
 D.室友关系；</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>00270_多选题
 下面哪些有关睡懒觉的说法是错误的是？（     ）
@@ -5000,14 +4983,14 @@
 D.延长社会性睡眠延迟；</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>00271_多选题
 电子游戏作为现代生活中的一种娱乐方式，它的模拟功能可以帮助我们？（     ）
@@ -5017,14 +5000,14 @@
 D.激发创造力和解决问题的能力；</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>00272_多选题
 学生帮助教师有哪些益处？（     ）
@@ -5034,14 +5017,14 @@
 D.降低学生的学业成绩；</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>00273_多选题
 温暖会带给人很多感觉，下列说法中错误的是？（     ）
@@ -5051,14 +5034,14 @@
 D.不可预测；</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>00274_多选题
 深入理解教材对教学过程的影响包括哪些？（     ）
@@ -5068,14 +5051,14 @@
 D.优化课堂教学，实现系统的整体优化；</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>00275_多选题
 教师可以有意识指导大学生进行放松训练，自我减压，以下说法正确的是？（     ）
@@ -5085,14 +5068,14 @@
 D.可以提供专业心理辅导、建立放松空间等；</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>00276_多选题
 情绪稳定的大学生面对挑战时更有可能出现何种表现？（     ）
@@ -5102,14 +5085,14 @@
 D.流畅沟通；</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>00277_多选题
 以下关于淡化个别考试结果，注重具体过程说法正确的是？（     ）
@@ -5119,14 +5102,14 @@
 D.教师应帮助学生建立健康的学习态度和应对压力的能力；</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>00278_多选题
 大学生在完成情绪调节的实施阶段时通常涉及哪两个过程？（     ）
@@ -5136,14 +5119,14 @@
 D.监控；</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>00279_多选题
 教师不恰当教学行为产生的原因包括哪些？（     ）
@@ -5153,14 +5136,14 @@
 D.教师共情疲劳；</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>00280_多选题
 具有攻击型竞争心理的大学生可能会表现出哪些行为？（     ）
@@ -5170,14 +5153,14 @@
 D.伤害自己或他人；</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>00281_多选题
 哪些视觉和文本处理技巧能有效辅助大学生理解和记忆教学内容？（     ）
@@ -5187,14 +5170,14 @@
 D.利用斜体字突出重要概念；</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>00282_多选题
 当教师资格证考试因疫情取消时，能灵活运用认知重评策略的大学生会表现出哪些表现？（     ）
@@ -5204,14 +5187,14 @@
 D.完全心灰意冷；</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>00283_多选题
 根据耶克斯-多德森定律，下面哪种任务最适合大学生可以适当降低自己的动机水平来应对？（     ）
@@ -5221,14 +5204,14 @@
 D.一个星期通过司法考试；</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>BD</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>00284_多选题
 为帮助学生确立既具有挑战性又是切实可行的目标，大学教师可以遵循哪些SMART原则来进行教学？（     ）
@@ -5238,14 +5221,14 @@
 D.可衡量性；</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>00285_多选题
 光环效应与下列哪些常见的俗语或表达方式相似？（     ）
@@ -5255,14 +5238,14 @@
 D.百无一害；</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>00286_多选题
 大学生长时间使用手机和电脑可能会引发哪些问题？（     ）
@@ -5272,14 +5255,14 @@
 D.产生易怒倾向；</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B285" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>00287_多选题
 大学生的目标感作为一种自我驱动的生活目标，通常具有哪些特征？（     ）
@@ -5289,31 +5272,14 @@
 D.与自我评估的价值不同；</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B286" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>00288_多选题
-大学教师在课堂上的言语表达有应注意哪些？（     ）（该题目已移除！）
-A.教师可通过适当放慢语速以提高信息传递量；
-B.教师可使用简单句来帮助学生理解复杂知识点；
-C.教师应尽可能多地使用专业术语；
-D.教师应避免使用任何肢体语言；</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>00289_多选题
 大学教师引导学生战胜“手机分离焦虑”，可以通过哪些方式？（     ）
@@ -5323,14 +5289,14 @@
 D.鼓励学生多上网，玩网络游戏；</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>00290_多选题
 焦虑是一种复杂情绪，是指个体对即将来临的、可能会造成的危险或威胁所产生的哪些状态？（     ）
@@ -5340,14 +5306,14 @@
 D.兴奋；</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>00291_多选题
 同伴关系是个体在社会交往过程中建立和发展起来的一种人际关系，通常发生在？（     ）
@@ -5357,14 +5323,14 @@
 D.年龄差距巨大个体之间；</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>00292_多选题
 成长型思维干预的目的包括哪些？（     ）
@@ -5374,14 +5340,14 @@
 D.改变人们对逆境的解释；</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>00293_多选题
 倾听的关键是什么？（     ）
@@ -5391,14 +5357,14 @@
 D.只关注优秀学生；</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>00294_多选题
 大学生如何做到科学地运动？（     ）
@@ -5408,14 +5374,14 @@
 D.运动时循序渐进和量力而行；</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>00295_多选题
 该如何引导大学生建立良好的室友关系？（     ）
@@ -5425,14 +5391,14 @@
 D.引导学生培养受欢迎的人格特质；</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>00296_多选题
 大学新教师在职业适应过程中常见的问题类型包括哪些？（     ）
@@ -5442,14 +5408,14 @@
 D.亲子关系适应问题；</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
+      <c r="B294" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>00297_多选题
 主观幸福感是个体依据自我内化的标准对其生活质量做出的整体性判断，具有哪些特征？（     ）
@@ -5459,14 +5425,14 @@
 D.唯一性；</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
+      <c r="B295" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
+    <row r="296">
+      <c r="A296" t="inlineStr">
         <is>
           <t>00298_多选题
 良好的同伴关系能够为大学生提供必要的情感支持并能带来哪些益处？（     ）
@@ -5476,14 +5442,14 @@
 D.增加焦虑症状；</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B296" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>00299_多选题
 高外倾性的大学生更乐于与他人建立友好关系，因为他们通常持有哪些态度？（     ）
@@ -5493,14 +5459,14 @@
 D.友好；</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
+    <row r="298">
+      <c r="A298" t="inlineStr">
         <is>
           <t>00300_多选题
 心理学“知−行−信”课程思政模式的实施层面包括哪些？（     ）
@@ -5510,14 +5476,14 @@
 D.学以致用；</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
+    <row r="299">
+      <c r="A299" t="inlineStr">
         <is>
           <t>00301_多选题
 大脑的哪些区域通常与执行功能和运动控制有关？（     ）
@@ -5527,14 +5493,14 @@
 D.前额顶网络；</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
+    <row r="300">
+      <c r="A300" t="inlineStr">
         <is>
           <t>00302_多选题
 国家级一流本科课程包括哪些类型的课程？（     ）
@@ -5544,14 +5510,14 @@
 D.社会实践课程；</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
+    <row r="301">
+      <c r="A301" t="inlineStr">
         <is>
           <t>00303_多选题
 教师该如何帮助沉浸于暴力游戏的大学生进行认知重构？（     ）
@@ -5561,14 +5527,14 @@
 D.禁止他们继续玩暴力游戏；</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>00304_多选题
 马斯洛将人的五种基本需要划分为成长性需要和缺失性需要两大类，下列选项属于缺失性需要的是哪些？（     ）
@@ -5578,14 +5544,14 @@
 D.尊重需要；</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
+    <row r="303">
+      <c r="A303" t="inlineStr">
         <is>
           <t>00305_多选题
 年龄影响主观幸福感主要体现在？（     ）
@@ -5595,14 +5561,14 @@
 D.成人期理性判断限制了感恩体验和行为，主观幸福感也相应较高；</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
+    <row r="304">
+      <c r="A304" t="inlineStr">
         <is>
           <t>00306_多选题
 哪些因素或现象与内源性大麻素系统有关？（     ）
@@ -5612,14 +5578,14 @@
 D.运动；</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
+    <row r="305">
+      <c r="A305" t="inlineStr">
         <is>
           <t>00307_多选题
 饥饿时，我们应选择哪些易于消化的清淡食物？（     ）
@@ -5629,14 +5595,14 @@
 D.酒精；</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>00308_多选题
 大学生自我妨碍行为的特点通常包括哪些方面？（     ）
@@ -5646,14 +5612,14 @@
 D.个体避免将失败原因归咎于自己的能力不足；</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
+    <row r="307">
+      <c r="A307" t="inlineStr">
         <is>
           <t>00309_多选题
 大学生在进行道歉时，需要注意哪些要点？（     ）
@@ -5663,14 +5629,14 @@
 D.要采取实际行动做出补救；</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
+      <c r="B307" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
+    <row r="308">
+      <c r="A308" t="inlineStr">
         <is>
           <t>00310_多选题
 以下哪些表述是正确的？（     ）
@@ -5680,14 +5646,14 @@
 D.一名大学教师如果没有学科团队意识，就容易在原地踏步，甚至退步；</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
+    <row r="309">
+      <c r="A309" t="inlineStr">
         <is>
           <t>00311_多选题
 教师在处理教材时可以采取哪些创造性的方法？（     ）
@@ -5697,14 +5663,14 @@
 D.以上都不是；</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>00312_多选题
 运动时确保安全和效果的关键原则主要包括？（     ）
@@ -5714,14 +5680,14 @@
 D.结伴运动；</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>00313_多选题
 下列哪项措施能有效干预大学生的自我妨碍行为？（     ）
@@ -5731,14 +5697,14 @@
 D.关注自身的不足；</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>00314_多选题
 大学教师可以通过以下哪些措施增强学生的自我决定感？（     ）
@@ -5748,14 +5714,14 @@
 D.设置课堂辩论环节；</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>00315_多选题
 以下哪种措施能帮助大学生建立正确的归因模式？（     ）
@@ -5765,14 +5731,14 @@
 D.只关注学生的成绩；</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>00316_多选题
 过度的同辈压力可能导致大学生出现哪些后果？（     ）
@@ -5782,14 +5748,14 @@
 D.自尊心受损；</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
+    <row r="315">
+      <c r="A315" t="inlineStr">
         <is>
           <t>00317_多选题
 相似性原则指的是人们在交往过程中，如果双方在哪些方面具有相似性或一致性，就容易产生相互吸引？（     ）
@@ -5799,14 +5765,14 @@
 D.人格特质；</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>00318_多选题
 持有固定型思维模式的大学生通常展现出哪些特征？（     ）
@@ -5816,14 +5782,14 @@
 D.认为努力是缺乏天赋的标志；</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>00319_多选题
 以下关于教师该如何引导学生发展目标感的说法，正确的是？（     ）
@@ -5833,14 +5799,14 @@
 D.以核心价值观来指导他们的行为和决策；</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>00320_多选题
 大学生具备理性竞争意识有助于他们追求卓越和持续发展。那么，如何培养大学生的理性竞争意识？（     ）
@@ -5850,14 +5816,14 @@
 D.培养学生人际交往能力；</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>00321_多选题
 大学生感到同辈压力，为了适应同辈群体的规范，可能会表现出以下哪些倾向？（     ）
@@ -5867,14 +5833,14 @@
 D.改变运势；</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>00322_多选题
 大学生不良情绪的成因包括客观原因和主观原因，其中主观原因包括？（     ）
@@ -5884,14 +5850,14 @@
 D.生活琐事；</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>00323_多选题
 韦纳的归因理论认为个体对行为成败原因的分析主要包括？（     ）
@@ -5901,14 +5867,14 @@
 D.运气；</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>00324_多选题
 大学生在进行情绪调节时，通常包括哪些阶段？（     ）
@@ -5918,14 +5884,14 @@
 D.后测阶段；</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>00325_多选题
 大学生长期处于高竞争压力的环境中可能会导致哪些后果？（     ）
@@ -5935,14 +5901,14 @@
 D.抑郁倾向提高；</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>00326_多选题
 德西的自我决定理论将人类行为归类为哪些类型？（     ）
@@ -5952,14 +5918,14 @@
 D.利己行为；</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
+    <row r="325">
+      <c r="A325" t="inlineStr">
         <is>
           <t>00327_多选题
 情境选择是情绪调节中最具前瞻性的方式，大学生小明熟练掌握该种策略，具体表现为？（     ）
@@ -5969,14 +5935,14 @@
 D.小明需要在会议上公开报告，他选择反复背诵练习；</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>00328_多选题
 在讲授过程中，大学教师应当注意哪些要点？（     ）
@@ -5986,14 +5952,14 @@
 D.保持高冷状态；</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>00329_多选题
 感恩记录中，感恩的对象可以是？（     ）
@@ -6003,14 +5969,14 @@
 D.自然；</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>00330_多选题
 心理学的主要目标是"（     ）"个体心理与行为。
@@ -6020,14 +5986,14 @@
 D.控制；</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>00331_多选题
 教师如何做到关爱？（     ）
@@ -6037,14 +6003,14 @@
 D.身体前倾；</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>00332_多选题
 “行”的层面需要做到哪些？（     ）
@@ -6054,14 +6020,14 @@
 D.加强社会服务实践；</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>00333_多选题
 以下哪些是有效的道歉方式？（     ）
@@ -6071,14 +6037,14 @@
 D.“这件事怪我，我会改正的。”；</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>00334_多选题
 教师向学生道歉有哪些好处？（     ）
@@ -6088,14 +6054,14 @@
 D.增强教师权威；</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
+    <row r="333">
+      <c r="A333" t="inlineStr">
         <is>
           <t>00335_多选题
 关于大学教师的不恰当教学行为，从学生和教师两个角度来看，可以概括为哪些方面？（     ）
@@ -6105,14 +6071,14 @@
 D.对学生的态度冷漠；</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
+    <row r="334">
+      <c r="A334" t="inlineStr">
         <is>
           <t>00336_多选题
 美国心理学家加德纳和斯坦博格2005年的一项同辈压力研究发现？（     ）
@@ -6122,14 +6088,14 @@
 D.成年组比少年组和青年组更激进；</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
+    <row r="335">
+      <c r="A335" t="inlineStr">
         <is>
           <t>00337_多选题
 根据中南大学精神卫生研究所的长期跟踪研究结果，长时间使用手机电脑等设备可能对大学生产生什么影响？（     ）
@@ -6139,31 +6105,14 @@
 D.建立良好同辈关系；</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>00338_多选题
-温暖会给人很多感觉，下列说法中错误的是？（     ）（该题目已移除！）
-A.亲近感；
-B.距离感；
-C.神秘感；
-D.不可预测；</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>BCD</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>00339_多选题
 大学教师可以通过以下哪些方式加强自我关爱并避免共情疲劳的发生？（     ）
@@ -6173,14 +6122,14 @@
 D.增加工作时间；</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
+    <row r="337">
+      <c r="A337" t="inlineStr">
         <is>
           <t>00340_多选题
 在大学生进行剧烈运动时，哪些神经递质的水平可能会上升？（     ）
@@ -6190,14 +6139,14 @@
 D.γ-氨基丁酸；</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
+    <row r="338">
+      <c r="A338" t="inlineStr">
         <is>
           <t>00341_多选题
 大学生需要学习和利用策略来调节自身情绪，这些情绪调节策略包括？（     ）
@@ -6207,14 +6156,14 @@
 D.认知改变；</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B338" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
+    <row r="339">
+      <c r="A339" t="inlineStr">
         <is>
           <t>00342_多选题
 通常来说，那些习惯记录感恩事项的大学生倾向于展现出以下哪些特点？（     ）
@@ -6224,14 +6173,14 @@
 D.更高的消极情感；</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B339" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
+    <row r="340">
+      <c r="A340" t="inlineStr">
         <is>
           <t>00343_多选题
 大学生通常会面临哪些压力？（     ）
@@ -6241,14 +6190,14 @@
 D.生涯规划；</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
+    <row r="341">
+      <c r="A341" t="inlineStr">
         <is>
           <t>00344_多选题
 根据德韦克的研究，大学生对能力的看法可以归纳为哪些类型的思维模式？（     ）
@@ -6258,14 +6207,14 @@
 D.开放型思维；</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
+    <row r="342">
+      <c r="A342" t="inlineStr">
         <is>
           <t>00345_多选题
 以下关于不同参与类型对大学生目标感的影响的说法，正确的是？（     ）
@@ -6275,14 +6224,14 @@
 D.实习和社会实践则通过深化自我认知，影响大学生的人生目标感；</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
+    <row r="343">
+      <c r="A343" t="inlineStr">
         <is>
           <t>00346_多选题
 大学生不正当竞争心理可划分为几种类型？（     ）
@@ -6292,14 +6241,14 @@
 D.逃避型竞争；</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B343" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
+    <row r="344">
+      <c r="A344" t="inlineStr">
         <is>
           <t>00347_多选题
 大学教师在课堂上的言语表达应注意哪些？（     ）
@@ -6309,14 +6258,14 @@
 D.教师应避免使用任何肢体语言；</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
+    <row r="345">
+      <c r="A345" t="inlineStr">
         <is>
           <t>00348_多选题
 根据动机的来源，动机可以分为哪几类？（     ）
@@ -6326,14 +6275,14 @@
 D.近景性动机；</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B345" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="346">
+      <c r="A346" t="inlineStr">
         <is>
           <t>00349_多选题
 大学教师可以用哪些措施帮助学生妥善应对压力？（     ）
@@ -6343,14 +6292,14 @@
 D.帮助学生淡化压力，让适度的压力化作前进的动力；</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
+    <row r="347">
+      <c r="A347" t="inlineStr">
         <is>
           <t>00350_多选题
 以下关于引导学生调整认知，制定合理目标说法正确的是？（     ）
@@ -6360,14 +6309,14 @@
 D.教师应该鼓励学生用辩证和发展的眼光看待自己；</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B347" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="348">
+      <c r="A348" t="inlineStr">
         <is>
           <t>00351_多选题
 在网络课程中，有大学教师露脸的视频课可能会产生哪些有利影响？（     ）
@@ -6377,14 +6326,14 @@
 D.监督保持学习；</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B348" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="349">
+      <c r="A349" t="inlineStr">
         <is>
           <t>00352_多选题
 习得性无助作为一种心理状态和行为模式，通常由哪些因素导致？（     ）
@@ -6394,14 +6343,14 @@
 D.缺乏积极的应对策略；</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr">
         <is>
           <t>00353_多选题
 大学教师活用手势可以促进其教学效果，手势在教学过程中有以下哪些作用？（     ）
@@ -6411,14 +6360,14 @@
 D.拉进师生距离；</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B350" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+    <row r="351">
+      <c r="A351" t="inlineStr">
         <is>
           <t>00354_多选题
 库纳尔的研究能够给大学生带来的启示是什么？（     ）
@@ -6428,14 +6377,14 @@
 D.保证一定的睡眠时间；</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
+    <row r="352">
+      <c r="A352" t="inlineStr">
         <is>
           <t>00355_多选题
 以下哪些观点反映了大学生对游戏暴力内容的正确理解？（     ）
@@ -6445,14 +6394,14 @@
 D.既享受暴力，也享受游戏中的成功体验；</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
+    <row r="353">
+      <c r="A353" t="inlineStr">
         <is>
           <t>00356_多选题
 哪些关于运动的观点是正确的？（     ）
@@ -6462,14 +6411,14 @@
 D.运动只会消耗体力；</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
+    <row r="354">
+      <c r="A354" t="inlineStr">
         <is>
           <t>00357_多选题
 “知−行−信”模式中的“知”包括哪些方面？（     ）
@@ -6479,14 +6428,14 @@
 D.实践活动；</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>00358_多选题
 成长型思维干预如何帮助学生应对压力？（     ）
@@ -6496,14 +6445,14 @@
 D.通过赋予人们解释和组织世界框架的能力；</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>AD</t>
         </is>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
+    <row r="356">
+      <c r="A356" t="inlineStr">
         <is>
           <t>00359_多选题
 在网络教学中，哪些因素可能会对大学教师的教学效果产生影响？（     ）
@@ -6513,14 +6462,14 @@
 D.教师形象的呈现与否；</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>00360_多选题
 网络成瘾可能给大学生带来哪些负面影响？（     ）
@@ -6530,14 +6479,14 @@
 D.心理健康问题；</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B357" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>00361_多选题
 向学生寻求帮助时，需要注意哪些技巧？（     ）
@@ -6547,14 +6496,14 @@
 D.不需要考虑学生的感受；</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>00362_多选题
 感恩可以分为特质感恩和状态感恩，其中状态感恩的特点包括？（     ）
@@ -6564,14 +6513,14 @@
 D.持续一段时间的心境；</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
+    <row r="360">
+      <c r="A360" t="inlineStr">
         <is>
           <t>00363_多选题
 大学生拥有以下哪些品质可能建立更稳固的人际关系？（     ）
@@ -6581,14 +6530,14 @@
 D.情绪稳定；</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
+    <row r="361">
+      <c r="A361" t="inlineStr">
         <is>
           <t>00364_多选题
 帮助他人能够给自己带来快乐，这种快乐主要体现在哪些方面？（     ）
@@ -6598,14 +6547,14 @@
 D.缓解生理疼痛；</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>00365_多选题
 下列哪些主张符合辩证唯物主义认识论？（     ）
@@ -6615,14 +6564,14 @@
 D.认识是实践发展的来源；</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="363">
+      <c r="A363" t="inlineStr">
         <is>
           <t>00366_多选题
 根据美国学者安德森的研究成果，拥有哪些特质的大学生更有人际吸引力？（     ）
@@ -6632,14 +6581,14 @@
 D.高抑郁质；</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="364">
+      <c r="A364" t="inlineStr">
         <is>
           <t>00367_多选题
 关于“高冷”的相关解释，以下哪些说法是正确的？（     ）
@@ -6649,14 +6598,14 @@
 D.该笑的时候，镇定自若；该哭的时候，隐忍克制；</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>BD</t>
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="365">
+      <c r="A365" t="inlineStr">
         <is>
           <t>00368_多选题
 以下关于教师向学生解释设定目标的重要性的说法，正确的是？（     ）
@@ -6666,14 +6615,14 @@
 D.说明将长远目标与近期目标结合的重要性；</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B365" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
+    <row r="366">
+      <c r="A366" t="inlineStr">
         <is>
           <t>00369_多选题
 学校通过教育游戏可以为大学生提供？（     ）
@@ -6683,14 +6632,14 @@
 D.暴力血腥的游戏体验；</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+    <row r="367">
+      <c r="A367" t="inlineStr">
         <is>
           <t>00370_多选题
 吃透教材的重要性体现在哪些方面？（     ）
@@ -6700,14 +6649,14 @@
 D.提升教师的教学技巧；</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
+    <row r="368">
+      <c r="A368" t="inlineStr">
         <is>
           <t>00371_多选题
 暴力在游戏中可能给大学生带来哪些负面影响？（     ）
@@ -6717,14 +6666,14 @@
 D.增加同情心；</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B368" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+    <row r="369">
+      <c r="A369" t="inlineStr">
         <is>
           <t>00372_多选题
 在网络课程中，有大学教师露脸的视频课可能会产生哪些不利影响？（     ）
@@ -6734,14 +6683,14 @@
 D.引导重点学习；</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
+    <row r="370">
+      <c r="A370" t="inlineStr">
         <is>
           <t>00373_多选题
 大学老师可以通过哪些方式引导学生合作？（     ）
@@ -6751,14 +6700,14 @@
 D.提供实践机会；</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
+    <row r="371">
+      <c r="A371" t="inlineStr">
         <is>
           <t>00374_多选题
 成长型思维干预对学生的长期影响可能包括哪些？（     ）
@@ -6768,14 +6717,14 @@
 D.提高学生的专业认同感与专业有用性；</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
+    <row r="372">
+      <c r="A372" t="inlineStr">
         <is>
           <t>00375_多选题
 合理的目标感有利于大学生理性竞争，大学老师应帮助学生树立怎样的目标感？（     ）
@@ -6785,14 +6734,14 @@
 D.遥不可及；</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
+    <row r="373">
+      <c r="A373" t="inlineStr">
         <is>
           <t>00376_多选题
 依据教育部及各级教育厅发布的教材管理办法，教师在教材选择上应考虑哪些因素？（     ）
@@ -6802,14 +6751,14 @@
 D.每个学生的个人喜好；</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
+    <row r="374">
+      <c r="A374" t="inlineStr">
         <is>
           <t>00377_多选题
 快速眼动阶段睡眠的作用主要包括？（     ）
@@ -6819,14 +6768,14 @@
 D.反刍所学内容；</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
+    <row r="375">
+      <c r="A375" t="inlineStr">
         <is>
           <t>00378_多选题
 美国学者安德森发现影响人际关系的人格品质有哪些？（     ）
@@ -6836,14 +6785,14 @@
 D.忠诚；</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="376">
+      <c r="A376" t="inlineStr">
         <is>
           <t>00379_多选题
 在网络教学中，教师应该如何有策略地露脸？（     ）
@@ -6854,14 +6803,14 @@
 E.持续评估和反馈；</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>ABCDE</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>00380_多选题
 教学中可以使用PPT动画效果可以潜在地表达知识点之间的哪些逻辑关系？（     ）
@@ -6871,14 +6820,14 @@
 D.否定；</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>00381_多选题
 自我妨碍作为一种心理策略，具有以下哪些功能？（     ）
@@ -6888,14 +6837,14 @@
 D.在成功时增强自我价值感；</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
+    <row r="379">
+      <c r="A379" t="inlineStr">
         <is>
           <t>00382_多选题
 马斯洛将人的五种基本需要划分为哪两大类？（     ）
@@ -6905,14 +6854,14 @@
 D.他人需要；</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
+    <row r="380">
+      <c r="A380" t="inlineStr">
         <is>
           <t>00383_多选题
 持有成长型思维的大学生通常展现出哪些特点？（     ）
@@ -6922,14 +6871,14 @@
 D.相信能力可以通过努力提升；</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
+    <row r="381">
+      <c r="A381" t="inlineStr">
         <is>
           <t>00384_多选题
 感恩可以提升大学生主观幸福感的原因包括？（     ）
@@ -6939,14 +6888,14 @@
 D.促进大学生为内在目标奋斗；</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B381" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
+    <row r="382">
+      <c r="A382" t="inlineStr">
         <is>
           <t>00385_多选题
 在道歉时，应该注意哪些方面？（     ）
@@ -6956,17 +6905,56 @@
 D.敢于道歉；</t>
         </is>
       </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>ABCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>00387_判断题
+目标感是一种有助于大学生在社交媒体环境中保持自尊稳定性的心理资源。</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>00388_判断题
+自我评估作为一种自我组织的生活目标，它能够组织和激励目标，管理行为，并提供意义感。</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>00389_判断题
+运动量的增加是导致“脆皮大学生”现象重要的原因之一。</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>ABCD</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>00386_判断题
-在教学过程当中，恰当的使用富兰克林效应，可以帮助我们提升更积极的共同经历来促进师生关系（该题目已移除！）</t>
+          <t>00390_判断题
+积极共同经历不仅能促进师生关系，还能够促进学生的个人发展</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -6978,21 +6966,21 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>00387_判断题
-目标感是一种有助于大学生在社交媒体环境中保持自尊稳定性的心理资源。</t>
+          <t>00391_判断题
+“知−行−信”模式的理论基础不包括辩证唯物主义。</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>00388_判断题
-自我评估作为一种自我组织的生活目标，它能够组织和激励目标，管理行为，并提供意义感。</t>
+          <t>00392_判断题
+一般来说，大学生的道歉其实不能修复人际信任。</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -7004,8 +6992,8 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>00389_判断题
-运动量的增加是导致“脆皮大学生”现象重要的原因之一。</t>
+          <t>00393_判断题
+根据张学民的研究结果，射杀行为比血腥场景更能显著提升大学生攻击性</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -7017,8 +7005,8 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>00390_判断题
-积极共同经历不仅能促进师生关系，还能够促进学生的个人发展</t>
+          <t>00394_判断题
+人是社会性动物无法离群索居，人际交往是我们生活中的重要部分。</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7030,21 +7018,21 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>00391_判断题
-“知−行−信”模式的理论基础不包括辩证唯物主义。</t>
+          <t>00395_判断题
+大学生在巨大同伴压力的影响之下可能会做出更多风险行为。</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>00392_判断题
-一般来说，大学生的道歉其实不能修复人际信任。</t>
+          <t>00396_判断题
+大学教师可以通过保持高冷的形象来维持自己教师的尊严。</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -7056,60 +7044,60 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>00393_判断题
-根据张学民的研究结果，射杀行为比血腥场景更能显著提升大学生攻击性</t>
+          <t>00397_判断题
+大学教师应选择适当的方式表达自己，这有助于维护其身心健康。</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>00394_判断题
-人是社会性动物无法离群索居，人际交往是我们生活中的重要部分。</t>
+          <t>00398_判断题
+无论什么学科，大学教师在指导学生时，先进行探索式教学再进行指导式教学的教学效果要优于先进行指导式教学再进行探索式教学。</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>00395_判断题
-大学生在巨大同伴压力的影响之下可能会做出更多风险行为。</t>
+          <t>00399_判断题
+大学教师在指导学生时，先进行指导式教学再进行探索式教学的教学效果优于先进行探索式教学再进行指导式教学。</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>00396_判断题
-大学教师可以通过保持高冷的形象来维持自己教师的尊严。</t>
+          <t>00400_判断题
+良性竞争可以激发大学生潜能。</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>00397_判断题
-大学教师应选择适当的方式表达自己，这有助于维护其身心健康。</t>
+          <t>00401_判断题
+大学教师团队的发展要建立在相互依赖、互帮互助的基础上。</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -7121,34 +7109,34 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>00398_判断题
-无论什么学科，大学教师在指导学生时，先进行探索式教学再进行指导式教学的教学效果要优于先进行指导式教学再进行探索式教学。</t>
+          <t>00402_判断题
+网络成瘾往往可以表现为大学生对网络使用的一种失控行为。</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>00399_判断题
-大学教师在指导学生时，先进行指导式教学再进行探索式教学的教学效果优于先进行探索式教学再进行指导式教学。</t>
+          <t>00403_判断题
+现实中的社会支持可以缓解网络成瘾带来的危害。</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>00400_判断题
-良性竞争可以激发大学生潜能。</t>
+          <t>00404_判断题
+学习线索的注意功能是指引导学习者注意PPT中特定的位置和信息。</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -7160,34 +7148,34 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>00401_判断题
-大学教师团队的发展要建立在相互依赖、互帮互助的基础上。</t>
+          <t>00405_判断题
+最早采用感恩记录方法来增加感恩的是塞利格曼等在2003年的一项研究。</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>00402_判断题
-网络成瘾往往可以表现为大学生对网络使用的一种失控行为。</t>
+          <t>00406_判断题
+大学生过分在意同辈的评价不会影响其心理健康和社交能力。</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>00403_判断题
-现实中的社会支持可以缓解网络成瘾带来的危害。</t>
+          <t>00407_判断题
+动机是指由需要引起并维持某种活动朝向某一目标的内在过程或内部心理状态。</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -7199,21 +7187,21 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>00404_判断题
-学习线索的注意功能是指引导学习者注意PPT中特定的位置和信息。</t>
+          <t>00408_判断题
+有氧运动可能不是以一种影响认知领域的方式对大脑连接性产生影响。</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>00405_判断题
-最早采用感恩记录方法来增加感恩的是塞利格曼等在2003年的一项研究。</t>
+          <t>00409_判断题
+在本我、自我和超我中，自我遵循的是快乐原则。</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -7225,8 +7213,8 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>00406_判断题
-大学生过分在意同辈的评价不会影响其心理健康和社交能力。</t>
+          <t>00410_判断题
+大学教师说话速度的快慢不会影响信息的传递量。</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -7238,8 +7226,8 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>00407_判断题
-动机是指由需要引起并维持某种活动朝向某一目标的内在过程或内部心理状态。</t>
+          <t>00411_判断题
+饥饿时应选择易于消化的清淡食物和适量饮水。</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -7251,8 +7239,8 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>00408_判断题
-有氧运动可能不是以一种影响认知领域的方式对大脑连接性产生影响。</t>
+          <t>00412_判断题
+大学教师应该保持高冷状态，这样有利于师生关系的建立。</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -7264,8 +7252,8 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>00409_判断题
-在本我、自我和超我中，自我遵循的是快乐原则。</t>
+          <t>00413_判断题
+耶克斯-多德森定律认为动机水平与工作效率之间的关系是一种U形曲线。</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -7277,21 +7265,21 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>00410_判断题
-大学教师说话速度的快慢不会影响信息的传递量。</t>
+          <t>00414_判断题
+患有“空心病”症状的大学生往往会感到内心空虚、缺乏生活目标和意义。</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>00411_判断题
-饥饿时应选择易于消化的清淡食物和适量饮水。</t>
+          <t>00415_判断题
+使用虚拟教师与形象有利于学生的学习。</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -7303,47 +7291,47 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>00412_判断题
-大学教师应该保持高冷状态，这样有利于师生关系的建立。</t>
+          <t>00416_判断题
+在自然的状态下，人体会在夜晚分泌褪黑色素来促进睡眠。</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>00413_判断题
-耶克斯-多德森定律认为动机水平与工作效率之间的关系是一种U形曲线。</t>
+          <t>00417_判断题
+长期的运动能够逆转我们激活的内源性大麻素系统，改善脂肪的代谢。</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>00414_判断题
-患有“空心病”症状的大学生往往会感到内心空虚、缺乏生活目标和意义。</t>
+          <t>00418_判断题
+竞争通常带来负面结果，大学生要避免竞争。</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>00415_判断题
-使用虚拟教师与形象有利于学生的学习。</t>
+          <t>00419_判断题
+高自我效能感是个体具有吸引力的显著特点之一，大学生应该注重自我开发，充分发展自身的潜能，以获得自信。</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -7355,8 +7343,8 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>00416_判断题
-在自然的状态下，人体会在夜晚分泌褪黑色素来促进睡眠。</t>
+          <t>00420_判断题
+“美丽就是好”是光环效应的一种表现。</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -7368,21 +7356,21 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>00417_判断题
-长期的运动能够逆转我们激活的内源性大麻素系统，改善脂肪的代谢。</t>
+          <t>00421_判断题
+大学教师与学生之间建立过于亲密的关系有利于学生的独立性发展。</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>00418_判断题
-竞争通常带来负面结果，大学生要避免竞争。</t>
+          <t>00422_判断题
+个体不同的归因方式不会产生不同的影响。</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -7394,8 +7382,8 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>00419_判断题
-高自我效能感是个体具有吸引力的显著特点之一，大学生应该注重自我开发，充分发展自身的潜能，以获得自信。</t>
+          <t>00423_判断题
+教师应当具备学科团队意识，处理好自己和团队的关系。</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -7407,8 +7395,8 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>00420_判断题
-“美丽就是好”是光环效应的一种表现。</t>
+          <t>00424_判断题
+如果教师没有吃透教材，他们将很难发现和处理课堂上的突发状况。</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -7420,8 +7408,8 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>00421_判断题
-大学教师与学生之间建立过于亲密的关系有利于学生的独立性发展。</t>
+          <t>00425_判断题
+当个体面临被评价的威胁时，人们不会通过拖延来进行自我妨碍。</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -7433,21 +7421,21 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>00422_判断题
-个体不同的归因方式不会产生不同的影响。</t>
+          <t>00426_判断题
+根据助人行为的正反馈循环，教师在请求学生帮助时应该掌握一定的技巧，并给予适当的感谢和反馈。</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>00423_判断题
-教师应当具备学科团队意识，处理好自己和团队的关系。</t>
+          <t>00427_判断题
+音乐陪伴下进行锻炼有利于提高情绪、减少疲劳感。</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -7459,21 +7447,21 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>00424_判断题
-如果教师没有吃透教材，他们将很难发现和处理课堂上的突发状况。</t>
+          <t>00428_判断题
+同辈压力对于大学生只有负面影响，没有积极作用。</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>00425_判断题
-当个体面临被评价的威胁时，人们不会通过拖延来进行自我妨碍。</t>
+          <t>00429_判断题
+道歉是一种常见且极为有效的信任修复手段，只要道歉就能修复双方之间的信任水平。</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -7485,21 +7473,21 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>00426_判断题
-根据助人行为的正反馈循环，教师在请求学生帮助时应该掌握一定的技巧，并给予适当的感谢和反馈。</t>
+          <t>00430_判断题
+相较于正常表达情绪个体来说，“高冷”的人（抑制情绪表达），更容易获得更高的社会支持以及人际关系满意。</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>00427_判断题
-音乐陪伴下进行锻炼有利于提高情绪、减少疲劳感。</t>
+          <t>00431_判断题
+自我反思是避免不恰当教学行为策略中的一个重要环节。</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -7511,34 +7499,34 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>00428_判断题
-同辈压力对于大学生只有负面影响，没有积极作用。</t>
+          <t>00432_判断题
+有研究结果发现，社会性微笑会使得丘脑、尾状核和前脑区的内啡肽的释放显著增加，而这些部位均与兴奋和情绪感知有关。</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>00429_判断题
-道歉是一种常见且极为有效的信任修复手段，只要道歉就能修复双方之间的信任水平。</t>
+          <t>00433_判断题
+情绪调节策略中的反应调整策略，是指直接改变情绪体验的生理反应。</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>00430_判断题
-相较于正常表达情绪个体来说，“高冷”的人（抑制情绪表达），更容易获得更高的社会支持以及人际关系满意。</t>
+          <t>00434_判断题
+大学教师过多运用教育制度的威信不会造成师生之间的冲突。</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -7550,8 +7538,8 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>00431_判断题
-自我反思是避免不恰当教学行为策略中的一个重要环节。</t>
+          <t>00435_判断题
+感恩是“美德之源”，且与个体主观幸福感密切相关。</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -7563,34 +7551,34 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>00432_判断题
-有研究结果发现，社会性微笑会使得丘脑、尾状核和前脑区的内啡肽的释放显著增加，而这些部位均与兴奋和情绪感知有关。</t>
+          <t>00436_判断题
+德西效应强调外部奖励可以增强内部动机。</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>00433_判断题
-情绪调节策略中的反应调整策略，是指直接改变情绪体验的生理反应。</t>
+          <t>00437_判断题
+教材是学生获取知识的唯一来源。</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>00434_判断题
-大学教师过多运用教育制度的威信不会造成师生之间的冲突。</t>
+          <t>00438_判断题
+大学教师在课堂教学过程中过多进行自我表露，有助于获得学生的积极评价。</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -7602,8 +7590,8 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>00435_判断题
-感恩是“美德之源”，且与个体主观幸福感密切相关。</t>
+          <t>00439_判断题
+压力具有双面性。</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -7615,21 +7603,21 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>00436_判断题
-德西效应强调外部奖励可以增强内部动机。</t>
+          <t>00440_判断题
+成年人进行感恩行为时，通常会进行更多的理性判断和选择。</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>00437_判断题
-教材是学生获取知识的唯一来源。</t>
+          <t>00441_判断题
+PPT的内容为王，设计的“花枝招展”和“素面朝天”对学生学习的影响都不大。</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -7641,8 +7629,8 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>00438_判断题
-大学教师在课堂教学过程中过多进行自我表露，有助于获得学生的积极评价。</t>
+          <t>00442_判断题
+培养大学生成长型思维时应该侧重于比较，而非强调个人发展和自我超越。</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -7654,21 +7642,21 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>00439_判断题
-压力具有双面性。</t>
+          <t>00443_判断题
+共生效应最早源于动物间相互影响、相互促进的现象。</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>00440_判断题
-成年人进行感恩行为时，通常会进行更多的理性判断和选择。</t>
+          <t>00444_判断题
+在网络教学中，教师应根据学生的个体差异来调整教师在视频中的呈现方式。</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -7680,34 +7668,34 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>00441_判断题
-PPT的内容为王，设计的“花枝招展”和“素面朝天”对学生学习的影响都不大。</t>
+          <t>00445_判断题
+教师的共情疲劳可能会导致他们在情感上出现压抑、沮丧、衰竭等异常症状。</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>00442_判断题
-培养大学生成长型思维时应该侧重于比较，而非强调个人发展和自我超越。</t>
+          <t>00446_判断题
+徐凯文指出，空心病主要是指那些成功被名校录取的大学生，进校学习时却“心空如也”，生活毫无目标感。</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>00443_判断题
-共生效应最早源于动物间相互影响、相互促进的现象。</t>
+          <t>00447_判断题
+人类大脑可在小时级内完成面孔特征和结构的编码，这使得大学生不可能在眨眼间判断出一张脸是不是美的。</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -7719,21 +7707,21 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>00444_判断题
-在网络教学中，教师应根据学生的个体差异来调整教师在视频中的呈现方式。</t>
+          <t>00448_判断题
+睡前用看书替代电子产品等方法，不能调节我们的睡眠规律。</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>00445_判断题
-教师的共情疲劳可能会导致他们在情感上出现压抑、沮丧、衰竭等异常症状。</t>
+          <t>00449_判断题
+根据班杜拉的研究结果，我们得知攻击行为可以被习得。</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -7745,8 +7733,8 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>00446_判断题
-徐凯文指出，空心病主要是指那些成功被名校录取的大学生，进校学习时却“心空如也”，生活毫无目标感。</t>
+          <t>00450_判断题
+师生间保持支持性的氛围有利于大学生理解合作的意义。</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -7758,8 +7746,8 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>00447_判断题
-人类大脑可在小时级内完成面孔特征和结构的编码，这使得大学生不可能在眨眼间判断出一张脸是不是美的。</t>
+          <t>00451_判断题
+大学教师的学术属性比诸如师生关系这类社会属性更为重要。</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -7771,8 +7759,8 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>00448_判断题
-睡前用看书替代电子产品等方法，不能调节我们的睡眠规律。</t>
+          <t>00452_判断题
+情绪调节策略中的情景修正是关于如何以不同的视角来看待已经产生的情绪。</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -7784,8 +7772,8 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>00449_判断题
-根据班杜拉的研究结果，我们得知攻击行为可以被习得。</t>
+          <t>00453_判断题
+大学教师表达自己的想法时需要考虑方式方法。</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -7797,47 +7785,47 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>00450_判断题
-师生间保持支持性的氛围有利于大学生理解合作的意义。</t>
+          <t>00454_判断题
+自我妨碍行为作为个体在遭遇评价威胁时不常见的一种自我保护行为。</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>00451_判断题
-大学教师的学术属性比诸如师生关系这类社会属性更为重要。</t>
+          <t>00455_判断题
+大学生的感恩培养可以通过感恩记录和感恩表达等方式。</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>00452_判断题
-情绪调节策略中的情景修正是关于如何以不同的视角来看待已经产生的情绪。</t>
+          <t>00456_判断题
+自我妨碍指大学生有意采取一些阻碍成功的行为来影响自己的表现，以便在失败时将原因归咎于这些因素。</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>00453_判断题
-大学教师表达自己的想法时需要考虑方式方法。</t>
+          <t>00457_判断题
+大学师生之间应该保持亲而有“间”的关系。</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -7849,47 +7837,47 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>00454_判断题
-自我妨碍行为作为个体在遭遇评价威胁时不常见的一种自我保护行为。</t>
+          <t>00458_判断题
+大学生内卷源于自身对资源过度争夺、对成功过度渴望的心理。</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>00455_判断题
-大学生的感恩培养可以通过感恩记录和感恩表达等方式。</t>
+          <t>00459_判断题
+行动式自我妨碍是指个体预先采取的一系列对成功有利的行为策略。</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>00456_判断题
-自我妨碍指大学生有意采取一些阻碍成功的行为来影响自己的表现，以便在失败时将原因归咎于这些因素。</t>
+          <t>00460_判断题
+大学生习惯于网络聊天，面对面交流的能力会得到显著提升。</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>00457_判断题
-大学师生之间应该保持亲而有“间”的关系。</t>
+          <t>00461_判断题
+大学生在人际交往过程中不应只看外貌，也应注重他人的内在品质。</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -7901,8 +7889,8 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>00458_判断题
-大学生内卷源于自身对资源过度争夺、对成功过度渴望的心理。</t>
+          <t>00462_判断题
+课程思政是中国高等教育中至关重要的一部分。</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -7914,8 +7902,8 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>00459_判断题
-行动式自我妨碍是指个体预先采取的一系列对成功有利的行为策略。</t>
+          <t>00463_判断题
+成长型思维对大学生应对压力、提升学业成绩的干预效果没有固定型思维好。</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -7927,34 +7915,34 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>00460_判断题
-大学生习惯于网络聊天，面对面交流的能力会得到显著提升。</t>
+          <t>00464_判断题
+案例分析和分享研讨是规范教师言语行为的有效方式。</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>00461_判断题
-大学生在人际交往过程中不应只看外貌，也应注重他人的内在品质。</t>
+          <t>00465_判断题
+长期的高竞争压力可能降低大学生的抑郁倾向。</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>00462_判断题
-课程思政是中国高等教育中至关重要的一部分。</t>
+          <t>00466_判断题
+自我妨碍是为了保护和提高个体的自尊。</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -7966,8 +7954,8 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>00463_判断题
-成长型思维对大学生应对压力、提升学业成绩的干预效果没有固定型思维好。</t>
+          <t>00467_判断题
+大学生所承受的压力就是他们的动力，所以没有压力就等于没有动力。</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -7979,21 +7967,21 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>00464_判断题
-案例分析和分享研讨是规范教师言语行为的有效方式。</t>
+          <t>00468_判断题
+大学教师说话速度越快传递的有效信息越多。</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>00465_判断题
-长期的高竞争压力可能降低大学生的抑郁倾向。</t>
+          <t>00469_判断题
+道歉是一种常见且极为有效的信任修复方式，只要道歉就一定能修复双方之间的信任水平。</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -8005,34 +7993,34 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>00466_判断题
-自我妨碍是为了保护和提高个体的自尊。</t>
+          <t>00470_判断题
+采用物质奖励是大学教师可以激发大学生内部学习动机的最有效方法。</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>00467_判断题
-大学生所承受的压力就是他们的动力，所以没有压力就等于没有动力。</t>
+          <t>00471_判断题
+同伴关系能有效衡量大学生群体身心健康以及社会适应水平。</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>00468_判断题
-大学教师说话速度越快传递的有效信息越多。</t>
+          <t>00472_判断题
+真诚的大学生通常给他人留下消极的印象。</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -8044,47 +8032,47 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>00469_判断题
-道歉是一种常见且极为有效的信任修复方式，只要道歉就一定能修复双方之间的信任水平。</t>
+          <t>00473_判断题
+“知−行−信”模式中的“知”是“行”的基础，“行”是“信”的支撑。</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>00470_判断题
-采用物质奖励是大学教师可以激发大学生内部学习动机的最有效方法。</t>
+          <t>00474_判断题
+大学生保持良好的人际关系有利于他们的身心健康。</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>00471_判断题
-同伴关系能有效衡量大学生群体身心健康以及社会适应水平。</t>
+          <t>00475_判断题
+教学过程本质上是一个不可控制的信息传递过程。</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>00472_判断题
-真诚的大学生通常给他人留下消极的印象。</t>
+          <t>00476_判断题
+心理学课程与思政课程没有一致性关系。</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -8096,8 +8084,8 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>00473_判断题
-“知−行−信”模式中的“知”是“行”的基础，“行”是“信”的支撑。</t>
+          <t>00477_判断题
+“詹森效应”指的是一个人平时表现良好，却由于缺乏应有的心理素质而导致竞技场上发挥失常。</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -8109,47 +8097,47 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>00474_判断题
-大学生保持良好的人际关系有利于他们的身心健康。</t>
+          <t>00478_判断题
+焦虑得不到缓解就会转化为躯体上的疾病，所以焦虑都是坏的。</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>00475_判断题
-教学过程本质上是一个不可控制的信息传递过程。</t>
+          <t>00479_判断题
+大学教师应持续评估教学方式的效果，以确保其有效性和适应性。</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>00476_判断题
-心理学课程与思政课程没有一致性关系。</t>
+          <t>00480_判断题
+教师设置合理的任务难度可以避免学生因过度受挫而学习动机下降。</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>00477_判断题
-“詹森效应”指的是一个人平时表现良好，却由于缺乏应有的心理素质而导致竞技场上发挥失常。</t>
+          <t>00481_判断题
+人体的生物钟节律与身体的免疫力息息相关。</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -8161,8 +8149,8 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>00478_判断题
-焦虑得不到缓解就会转化为躯体上的疾病，所以焦虑都是坏的。</t>
+          <t>00482_判断题
+暴力内容可以增进游戏体验。</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -8174,8 +8162,8 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>00479_判断题
-大学教师应持续评估教学方式的效果，以确保其有效性和适应性。</t>
+          <t>00483_判断题
+大学生协助教师的经历能够激发师生的积极互动，并促进双方关系。</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -8187,21 +8175,21 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>00480_判断题
-教师设置合理的任务难度可以避免学生因过度受挫而学习动机下降。</t>
+          <t>00484_判断题
+基于德韦克的研究结果，持大学生的能力不可改变的观点属于成长型思维。</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>00481_判断题
-人体的生物钟节律与身体的免疫力息息相关。</t>
+          <t>00485_判断题
+慢性运动有利于增加我们深度睡眠的时间，提高我们的睡眠质量。</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -8213,8 +8201,8 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>00482_判断题
-暴力内容可以增进游戏体验。</t>
+          <t>00486_判断题
+现代教育必须使用网络教学。</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -8226,8 +8214,8 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>00483_判断题
-大学生协助教师的经历能够激发师生的积极互动，并促进双方关系。</t>
+          <t>00487_判断题
+具身研究发现，大学生感受到的身体温度会影响其对他人人格特质的评价。</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -8239,8 +8227,8 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>00484_判断题
-基于德韦克的研究结果，持大学生的能力不可改变的观点属于成长型思维。</t>
+          <t>00488_判断题
+大学生自我妨碍的归因模式主要体现在稳定性维度上。</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -8252,8 +8240,8 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>00485_判断题
-慢性运动有利于增加我们深度睡眠的时间，提高我们的睡眠质量。</t>
+          <t>00489_判断题
+坚持是实现运动效果的核心要素。</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -8265,21 +8253,21 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>00486_判断题
-现代教育必须使用网络教学。</t>
+          <t>00490_判断题
+大学教师勇于表达自己的想法有利于自身的心理健康。</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>00487_判断题
-具身研究发现，大学生感受到的身体温度会影响其对他人人格特质的评价。</t>
+          <t>00491_判断题
+教师在教学中应该超越教材的字面意义，进行创新性拓展。</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -8291,21 +8279,21 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>00488_判断题
-大学生自我妨碍的归因模式主要体现在稳定性维度上。</t>
+          <t>00492_判断题
+同辈压力是大学生人际交往中的普遍现象。</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>00489_判断题
-坚持是实现运动效果的核心要素。</t>
+          <t>00493_判断题
+感恩记录指让个体定期记录一件或多件感恩事件。</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -8317,8 +8305,8 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>00490_判断题
-大学教师勇于表达自己的想法有利于自身的心理健康。</t>
+          <t>00494_判断题
+网络成瘾表现为过度使用互联网后，导致的明显学业、职业和社会性功能损伤。</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -8330,8 +8318,8 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>00491_判断题
-教师在教学中应该超越教材的字面意义，进行创新性拓展。</t>
+          <t>00495_判断题
+睡眠受到个体的生物钟节律的直接影响。</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -8343,8 +8331,8 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>00492_判断题
-同辈压力是大学生人际交往中的普遍现象。</t>
+          <t>00496_判断题
+不能合理分配教学资源的教师不利于创建良好的班级氛围。</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -8356,8 +8344,8 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>00493_判断题
-感恩记录指让个体定期记录一件或多件感恩事件。</t>
+          <t>00497_判断题
+教师应主动缩短和学生的心理距离，和学生成为朋友，让学生发自内心的尊重。</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -8369,8 +8357,8 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>00494_判断题
-网络成瘾表现为过度使用互联网后，导致的明显学业、职业和社会性功能损伤。</t>
+          <t>00498_判断题
+培养大学生成长型思维时应该侧重于强调个人发展和自我超越。</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -8382,8 +8370,8 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>00495_判断题
-睡眠受到个体的生物钟节律的直接影响。</t>
+          <t>00499_判断题
+大学教师团队的发展既要考虑团队整体的专业发展，也要考虑单个教师的个体发展。</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -8395,8 +8383,8 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>00496_判断题
-不能合理分配教学资源的教师不利于创建良好的班级氛围。</t>
+          <t>00500_判断题
+情境选择是情绪调节策略中，最具前瞻性的方式。</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -8408,8 +8396,8 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>00497_判断题
-教师应主动缩短和学生的心理距离，和学生成为朋友，让学生发自内心的尊重。</t>
+          <t>00501_判断题
+大学老师需要培养学生理性的竞争意识。</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -8421,47 +8409,47 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>00498_判断题
-培养大学生成长型思维时应该侧重于强调个人发展和自我超越。</t>
+          <t>00502_判断题
+大学生的网络朋友圈越大，自身孤独感可能越低。</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>00499_判断题
-大学教师团队的发展既要考虑团队整体的专业发展，也要考虑单个教师的个体发展。</t>
+          <t>00503_判断题
+对于大学教师而言，教材研发比教育教学更重要。</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>00500_判断题
-情境选择是情绪调节策略中，最具前瞻性的方式。</t>
+          <t>00504_判断题
+道歉是一种常见且极为有效的信任修复工具，只要道歉就一定能修复双方之间的信任水平。</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>00501_判断题
-大学老师需要培养学生理性的竞争意识。</t>
+          <t>00505_判断题
+面孔吸引力是指目标人物的面孔能诱发大学生产生积极的情绪体验，促进大学生产生接近他人的意愿。</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -8473,47 +8461,47 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>00502_判断题
-大学生的网络朋友圈越大，自身孤独感可能越低。</t>
+          <t>00506_判断题
+在教学过程当中，恰当的使用富兰克林效应，可以帮助我们提升更积极的共同经历来促进师生关系。</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>00503_判断题
-对于大学教师而言，教材研发比教育教学更重要。</t>
+          <t>00507_判断题
+心理学课程与思政课程具有同理性、同向性。</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>00504_判断题
-道歉是一种常见且极为有效的信任修复工具，只要道歉就一定能修复双方之间的信任水平。</t>
+          <t>00508_判断题
+在“电势能的正负判断”的课程中，教师先进行探索式教学再进行指导式教学的教学效果可能会优于先进行指导式教学再进行探索式教学。</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>00505_判断题
-面孔吸引力是指目标人物的面孔能诱发大学生产生积极的情绪体验，促进大学生产生接近他人的意愿。</t>
+          <t>00509_判断题
+师生之间保持适当的距离有助于彼此的互动。</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8525,8 +8513,8 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>00506_判断题
-在教学过程当中，恰当的使用富兰克林效应，可以帮助我们提升更积极的共同经历来促进师生关系。</t>
+          <t>00510_判断题
+教学内容与时俱进可以提高大学生的专业认同感与专业有用性。</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -8538,8 +8526,8 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>00507_判断题
-心理学课程与思政课程具有同理性、同向性。</t>
+          <t>00511_判断题
+富兰克林效应认为相比于那些接受过你帮助的人，曾帮助过你的人会更愿意帮助你。</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -8551,8 +8539,8 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>00508_判断题
-在“电势能的正负判断”的课程中，教师先进行探索式教学再进行指导式教学的教学效果可能会优于先进行指导式教学再进行探索式教学。</t>
+          <t>00512_判断题
+教师在网络教学中应该持续评估视频教学的效果，并根据学生的反馈进行调整。</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -8564,8 +8552,8 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>00509_判断题
-师生之间保持适当的距离有助于彼此的互动。</t>
+          <t>00513_判断题
+成长型思维干预不仅在实验室环境中有效，也能在现实生活的压力情境中减少个体的压力反应。</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -8577,34 +8565,34 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>00510_判断题
-教学内容与时俱进可以提高大学生的专业认同感与专业有用性。</t>
+          <t>00514_判断题
+耶克斯-多德森定律指出动机水平与工作效率之间的关系是一种M形曲线。</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>00511_判断题
-富兰克林效应认为相比于那些接受过你帮助的人，曾帮助过你的人会更愿意帮助你。</t>
+          <t>00515_判断题
+运动时的循序渐进和量力而行不是确保安全和效果的关键原则。</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>00512_判断题
-教师在网络教学中应该持续评估视频教学的效果，并根据学生的反馈进行调整。</t>
+          <t>00516_判断题
+大学教师在融入教学科研团队时，应尊重团队成员的学科背景、专业特长、研究领域和教学内容的差异化。</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -8616,102 +8604,50 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>00513_判断题
-成长型思维干预不仅在实验室环境中有效，也能在现实生活的压力情境中减少个体的压力反应。</t>
+          <t>00517_判断题
+大学教师的失范行为本质上都是违法行为。</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>00514_判断题
-耶克斯-多德森定律指出动机水平与工作效率之间的关系是一种M形曲线。</t>
+          <t>00518_判断题
+教育部发布的《高等学校课程思政建设指导纲要》强调了育人和育才的统一。</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>00515_判断题
-运动时的循序渐进和量力而行不是确保安全和效果的关键原则。</t>
+          <t>00519_判断题
+相比与中年人，大学生对感恩的体验与表达有较少的顾忌，主观幸福感也相应较高。</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>00516_判断题
-大学教师在融入教学科研团队时，应尊重团队成员的学科背景、专业特长、研究领域和教学内容的差异化。</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>00517_判断题
-大学教师的失范行为本质上都是违法行为。</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>错</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>00518_判断题
-教育部发布的《高等学校课程思政建设指导纲要》强调了育人和育才的统一。</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>00519_判断题
-相比与中年人，大学生对感恩的体验与表达有较少的顾忌，主观幸福感也相应较高。</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
           <t>00520_判断题
 适当的表露有助于学生对教师评价的提升。</t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>对</t>
         </is>
